--- a/requirements/procurement-ai-chat/data/source/price-book-Y2026.xlsx
+++ b/requirements/procurement-ai-chat/data/source/price-book-Y2026.xlsx
@@ -47219,7 +47219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -47286,12 +47286,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ธงญี่ปุ่น;feather flag;ธงชายธง</t>
+          <t>ธงญี่ปุ่น;feather flag;ธงชายธง;beach flag</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>PrintRate</t>
         </is>
       </c>
     </row>
@@ -47315,12 +47315,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ป้ายราคา</t>
+          <t>PP Board</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>shelf talker;ป้ายชั้นวาง;price card</t>
+          <t>โฟมบอร์ด;foam board;ป้ายโฟม;พีพีบอร์ด;พลาสวูด;plaswood</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -47332,12 +47332,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>โฟมบอร์ด</t>
+          <t>Shelf Talker</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>foam board;ป้ายโฟม</t>
+          <t>ป้ายราคา;ป้ายชั้นวาง;price card;ป้ายแขวน</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -47349,12 +47349,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>พลาสวูด</t>
+          <t>Vacuum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>plaswood;ป้ายพลาสวูด</t>
+          <t>ตู้เย็น;สติกเกอร์ตู้เย็น;cooler</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -47400,15 +47400,100 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ตู้เย็น</t>
+          <t>ไดคัท</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vacuum;สติกเกอร์ตู้เย็น;cooler</t>
+          <t>ไดคัด;diecut;die cut</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>PrintRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wrap Around</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ล้อมกอง;ป้ายล้อมกอง</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PrintRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ประกาศนียบัตร</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>เกียรติบัตร;certificate;วุฒิบัตร</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PrintRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>โปสเตอร์</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>poster;ใบปิด</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PrintRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ถังใส่น้ำแข็ง</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ถังน้ำแข็ง;ice bucket;ถังแช่</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>POSM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>หนังสือคู่มือ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>คู่มือ;booklet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>PrintRate</t>
         </is>

--- a/requirements/procurement-ai-chat/data/source/price-book-Y2026.xlsx
+++ b/requirements/procurement-ai-chat/data/source/price-book-Y2026.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U517"/>
+  <dimension ref="A1:U518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18326,9 +18326,6 @@
       <c r="L228" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="M228" t="e">
-        <v>#VALUE!</v>
-      </c>
       <c r="N228" s="5" t="n">
         <v>9</v>
       </c>
@@ -18349,12 +18346,12 @@
       </c>
       <c r="T228" s="4" t="inlineStr">
         <is>
-          <t>พิจารณาลำดับแรกจากราคาต่ำสุด(ระยะเวลาผลิต 15 วัน)หากเป็นความต้องการเร่งด่วนภายใน5-7 วัน พิจารณาซัพพลายเออร์ในท้องถิ่น</t>
+          <t>#VALUE! | พิจารณาลำดับแรกจากราคาต่ำสุด(ระยะเวลาผลิต 15 วัน)หากเป็นความต้องการเร่งด่วนภายใน5-7 วัน พิจารณาซัพพลายเออร์ในท้องถิ่น</t>
         </is>
       </c>
       <c r="U228" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-19] Wrap Around 3 mm. 70x100 cm. | รายละเอียด: วัสดุ PP Board 3 mm. พิมพ์ 1 ด้าน | ตัดสี่เหลี่ยม, พิมพ์ 4 สี | Indoor บน สติ๊กเกอร์ ติดบนแผ่น PP Board 3 mm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1001-2,000 ชิ้น | ราคาต่อหน่วย 115 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: #VALUE! | มีผู้เสนอราคา 9 ราย ต่ำสุด 115 สูงสุด 245 บาท | หมายเหตุ: พิจารณาลำดับแรกจากราคาต่ำสุด(ระยะเวลาผลิต 15 วัน)หากเป็นความต้องการเร่งด่วนภายใน5-7 วัน พิจารณาซัพพลายเออร์ในท้องถิ่น</t>
+          <t>[PrintRate-19] Wrap Around 3 mm. 70x100 cm. | รายละเอียด: วัสดุ PP Board 3 mm. พิมพ์ 1 ด้าน | ตัดสี่เหลี่ยม, พิมพ์ 4 สี | Indoor บน สติ๊กเกอร์ ติดบนแผ่น PP Board 3 mm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1001-2,000 ชิ้น | ราคาต่อหน่วย 115 บาท (ยังไม่รวม VAT 7%) | มีผู้เสนอราคา 9 ราย ต่ำสุด 115 สูงสุด 245 บาท | หมายเหตุ: #VALUE! | พิจารณาลำดับแรกจากราคาต่ำสุด(ระยะเวลาผลิต 15 วัน)หากเป็นความต้องการเร่งด่วนภายใน5-7 วัน พิจารณาซัพพลายเออร์ในท้องถิ่น</t>
         </is>
       </c>
     </row>
@@ -32267,11 +32264,6 @@
       <c r="J404" s="5" t="n"/>
       <c r="K404" s="5" t="n"/>
       <c r="L404" s="6" t="n"/>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
-        </is>
-      </c>
       <c r="N404" s="5" t="n">
         <v>4</v>
       </c>
@@ -32290,10 +32282,14 @@
           <t>{"vendor 7": 990, "vendor 9": 900, "vendor 12": 430, "vendor 14": 750}</t>
         </is>
       </c>
-      <c r="T404" s="4" t="n"/>
+      <c r="T404" s="4" t="inlineStr">
+        <is>
+          <t>พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
+        </is>
+      </c>
       <c r="U404" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-58.1] ฐานน้ำสำหรับธงปีกนก (Beach Flag) สีดำ ขนาด 20 L | หมวด: เรทงานพิมพ์ (Printing Rate) | ไม่มีราคาต่อหน่วยตายตัว ต้องอ้างอิงตามกฎในหมายเหตุ | ผู้ชนะประมูล: พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ | มีผู้เสนอราคา 4 ราย ต่ำสุด 430 สูงสุด 990 บาท</t>
+          <t>[PrintRate-58.1] ฐานน้ำสำหรับธงปีกนก (Beach Flag) สีดำ ขนาด 20 L | หมวด: เรทงานพิมพ์ (Printing Rate) | ไม่มีราคาต่อหน่วยตายตัว ต้องอ้างอิงตามกฎในหมายเหตุ | มีผู้เสนอราคา 4 ราย ต่ำสุด 430 สูงสุด 990 บาท | หมายเหตุ: พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
         </is>
       </c>
     </row>
@@ -32324,47 +32320,35 @@
         </is>
       </c>
       <c r="F405" s="4" t="n"/>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>น้อยกว่า 500</t>
-        </is>
-      </c>
-      <c r="J405" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K405" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L405" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>vendor 11</t>
-        </is>
-      </c>
+      <c r="J405" s="5" t="n"/>
+      <c r="K405" s="5" t="n"/>
+      <c r="L405" s="6" t="n"/>
       <c r="N405" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O405" s="6" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="P405" s="6" t="n">
-        <v>5.6</v>
+        <v>800</v>
       </c>
       <c r="Q405" s="6" t="n">
-        <v>4.3</v>
+        <v>440</v>
       </c>
       <c r="R405" s="6" t="n"/>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 9": 5.6, "vendor 11": 3}</t>
-        </is>
-      </c>
-      <c r="T405" s="4" t="n"/>
+          <t>{"vendor 7": 800, "vendor 9": 220, "vendor 12": 240, "vendor 14": 500}</t>
+        </is>
+      </c>
+      <c r="T405" s="4" t="inlineStr">
+        <is>
+          <t>พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
+        </is>
+      </c>
       <c r="U405" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-58.2] ฐานกากบาทสำหรับธงปีกนก | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน น้อยกว่า 500 ชิ้น | ราคาต่อหน่วย 3 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 3 สูงสุด 5.6 บาท</t>
+          <t>[PrintRate-58.2] ฐานกากบาทสำหรับธงปีกนก | หมวด: เรทงานพิมพ์ (Printing Rate) | ไม่มีราคาต่อหน่วยตายตัว ต้องอ้างอิงตามกฎในหมายเหตุ | มีผู้เสนอราคา 4 ราย ต่ำสุด 220 สูงสุด 800 บาท | หมายเหตุ: พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
         </is>
       </c>
     </row>
@@ -32471,11 +32455,7 @@
           <t>Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut</t>
         </is>
       </c>
-      <c r="F407" s="4" t="inlineStr">
-        <is>
-          <t>ตามแบบทำปลายมนบน 2 มุม</t>
-        </is>
-      </c>
+      <c r="F407" s="4" t="n"/>
       <c r="G407" t="n">
         <v>6</v>
       </c>
@@ -32484,45 +32464,45 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>1,001 - 1,500</t>
+          <t>น้อยกว่า 500</t>
         </is>
       </c>
       <c r="J407" s="5" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="K407" s="5" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="L407" s="6" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>vendor 5</t>
+          <t>vendor 11</t>
         </is>
       </c>
       <c r="N407" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O407" s="6" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="P407" s="6" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="Q407" s="6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="R407" s="6" t="n"/>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 5": 1.7, "vendor 9": 3.4, "vendor 11": 2.5, "vendor 14": 10}</t>
+          <t>{"vendor 9": 5.6, "vendor 11": 3}</t>
         </is>
       </c>
       <c r="T407" s="4" t="n"/>
       <c r="U407" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-59] Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut | รายละเอียด: ตามแบบทำปลายมนบน 2 มุม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 1.7 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 5 | มีผู้เสนอราคา 4 ราย ต่ำสุด 1.7 สูงสุด 10 บาท</t>
+          <t>[PrintRate-59] Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน น้อยกว่า 500 ชิ้น | ราคาต่อหน่วย 3 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 3 สูงสุด 5.6 บาท</t>
         </is>
       </c>
     </row>
@@ -32565,52 +32545,52 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>500 - 1,000</t>
+          <t>1,001 - 1,500</t>
         </is>
       </c>
       <c r="J408" s="5" t="n">
-        <v>500</v>
+        <v>1001</v>
       </c>
       <c r="K408" s="5" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="L408" s="6" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>vendor 11</t>
+          <t>vendor 5</t>
         </is>
       </c>
       <c r="N408" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O408" s="6" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="P408" s="6" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="Q408" s="6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="R408" s="6" t="n"/>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 11": 2.5, "vendor 15": 6.9}</t>
+          <t>{"vendor 5": 1.7, "vendor 9": 3.4, "vendor 11": 2.5, "vendor 14": 10}</t>
         </is>
       </c>
       <c r="T408" s="4" t="n"/>
       <c r="U408" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-59] Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut | รายละเอียด: ตามแบบทำปลายมนบน 2 มุม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 500 - 1,000 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 2.5 สูงสุด 6.9 บาท</t>
+          <t>[PrintRate-59] Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut | รายละเอียด: ตามแบบทำปลายมนบน 2 มุม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 1.7 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 5 | มีผู้เสนอราคา 4 ราย ต่ำสุด 1.7 สูงสุด 10 บาท</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>PrintRate-60</t>
+          <t>PrintRate-59</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -32625,28 +32605,38 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>สายรัดข้อมือ BIB 25x250 mm วัสดุกระดาษกันน้ำ เขียนไม่ลอก</t>
-        </is>
-      </c>
-      <c r="F409" s="4" t="n"/>
+          <t>Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut</t>
+        </is>
+      </c>
+      <c r="F409" s="4" t="inlineStr">
+        <is>
+          <t>ตามแบบทำปลายมนบน 2 มุม</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>6</v>
+      </c>
+      <c r="H409" t="n">
+        <v>5</v>
+      </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>1,001 - 2,000</t>
+          <t>500 - 1,000</t>
         </is>
       </c>
       <c r="J409" s="5" t="n">
-        <v>1001</v>
+        <v>500</v>
       </c>
       <c r="K409" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="L409" s="6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
@@ -32657,24 +32647,24 @@
         <v>2</v>
       </c>
       <c r="O409" s="6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="P409" s="6" t="n">
-        <v>5.75</v>
+        <v>6.9</v>
       </c>
       <c r="Q409" s="6" t="n">
-        <v>3.98</v>
+        <v>4.7</v>
       </c>
       <c r="R409" s="6" t="n"/>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 11": 2.2, "vendor 15": 5.75}</t>
+          <t>{"vendor 11": 2.5, "vendor 15": 6.9}</t>
         </is>
       </c>
       <c r="T409" s="4" t="n"/>
       <c r="U409" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-60] สายรัดข้อมือ BIB 25x250 mm วัสดุกระดาษกันน้ำ เขียนไม่ลอก | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 2,000 ชิ้น | ราคาต่อหน่วย 2.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 2.2 สูงสุด 5.75 บาท</t>
+          <t>[PrintRate-59] Riji ขนาด 6x5cm หนา 0.3 mm. พิมพ์4สี 1 หน้า เคลือบยูวี Diecut | รายละเอียด: ตามแบบทำปลายมนบน 2 มุม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 500 - 1,000 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 2.5 สูงสุด 6.9 บาท</t>
         </is>
       </c>
     </row>
@@ -32707,17 +32697,17 @@
       <c r="F410" s="4" t="n"/>
       <c r="I410" t="inlineStr">
         <is>
-          <t>2,001 - 3,000</t>
+          <t>1,001 - 2,000</t>
         </is>
       </c>
       <c r="J410" s="5" t="n">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="K410" s="5" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="L410" s="6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M410" t="inlineStr">
         <is>
@@ -32728,31 +32718,31 @@
         <v>2</v>
       </c>
       <c r="O410" s="6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P410" s="6" t="n">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q410" s="6" t="n">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="R410" s="6" t="n"/>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 11": 2, "vendor 15": 4.95}</t>
+          <t>{"vendor 11": 2.2, "vendor 15": 5.75}</t>
         </is>
       </c>
       <c r="T410" s="4" t="n"/>
       <c r="U410" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-60] สายรัดข้อมือ BIB 25x250 mm วัสดุกระดาษกันน้ำ เขียนไม่ลอก | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 2,001 - 3,000 ชิ้น | ราคาต่อหน่วย 2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 2 สูงสุด 4.95 บาท</t>
+          <t>[PrintRate-60] สายรัดข้อมือ BIB 25x250 mm วัสดุกระดาษกันน้ำ เขียนไม่ลอก | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 2,000 ชิ้น | ราคาต่อหน่วย 2.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 2.2 สูงสุด 5.75 บาท</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>PrintRate-61</t>
+          <t>PrintRate-60</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -32767,38 +32757,28 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>shelf stip 4x40 cm อาร์ตการ์ด300g</t>
-        </is>
-      </c>
-      <c r="F411" s="4" t="inlineStr">
-        <is>
-          <t>พิมพ์4สี จำนวน 1หน้า เคลือบ PVC</t>
-        </is>
-      </c>
-      <c r="G411" t="n">
-        <v>4</v>
-      </c>
-      <c r="H411" t="n">
-        <v>40</v>
-      </c>
+          <t>สายรัดข้อมือ BIB 25x250 mm วัสดุกระดาษกันน้ำ เขียนไม่ลอก</t>
+        </is>
+      </c>
+      <c r="F411" s="4" t="n"/>
       <c r="I411" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>2,001 - 3,000</t>
         </is>
       </c>
       <c r="J411" s="5" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="K411" s="5" t="n">
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="L411" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M411" t="inlineStr">
         <is>
@@ -32806,27 +32786,27 @@
         </is>
       </c>
       <c r="N411" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O411" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P411" s="6" t="n">
-        <v>37.4</v>
+        <v>4.95</v>
       </c>
       <c r="Q411" s="6" t="n">
-        <v>18.08</v>
+        <v>3.48</v>
       </c>
       <c r="R411" s="6" t="n"/>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 9": 37.4, "vendor 11": 10, "vendor 13": 11.5, "vendor 14": 20}</t>
+          <t>{"vendor 11": 2, "vendor 15": 4.95}</t>
         </is>
       </c>
       <c r="T411" s="4" t="n"/>
       <c r="U411" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 10 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 10 สูงสุด 37.4 บาท</t>
+          <t>[PrintRate-60] สายรัดข้อมือ BIB 25x250 mm วัสดุกระดาษกันน้ำ เขียนไม่ลอก | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 2,001 - 3,000 ชิ้น | ราคาต่อหน่วย 2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 2 ราย ต่ำสุด 2 สูงสุด 4.95 บาท</t>
         </is>
       </c>
     </row>
@@ -32869,45 +32849,45 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>51 - 99</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J412" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K412" s="5" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="L412" s="6" t="n">
-        <v>5.58</v>
+        <v>10</v>
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>vendor 6</t>
+          <t>vendor 11</t>
         </is>
       </c>
       <c r="N412" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O412" s="6" t="n">
-        <v>5.58</v>
+        <v>10</v>
       </c>
       <c r="P412" s="6" t="n">
-        <v>15.24</v>
+        <v>37.4</v>
       </c>
       <c r="Q412" s="6" t="n">
-        <v>9.91</v>
+        <v>18.08</v>
       </c>
       <c r="R412" s="6" t="n"/>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 5.58, "vendor 9": 15.24, "vendor 11": 8, "vendor 13": 5.75, "vendor 14": 15}</t>
+          <t>{"vendor 6": 11.5, "vendor 9": 37.4, "vendor 11": 10, "vendor 13": 11.5, "vendor 14": 20}</t>
         </is>
       </c>
       <c r="T412" s="4" t="n"/>
       <c r="U412" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 99 ชิ้น | ราคาต่อหน่วย 5.58 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 5.58 สูงสุด 15.24 บาท</t>
+          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 10 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 10 สูงสุด 37.4 บาท</t>
         </is>
       </c>
     </row>
@@ -32950,17 +32930,17 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>100 - 200</t>
+          <t>51 - 99</t>
         </is>
       </c>
       <c r="J413" s="5" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="K413" s="5" t="n">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="L413" s="6" t="n">
-        <v>4.43</v>
+        <v>5.58</v>
       </c>
       <c r="M413" t="inlineStr">
         <is>
@@ -32971,24 +32951,24 @@
         <v>5</v>
       </c>
       <c r="O413" s="6" t="n">
-        <v>4.43</v>
+        <v>5.58</v>
       </c>
       <c r="P413" s="6" t="n">
-        <v>10</v>
+        <v>15.24</v>
       </c>
       <c r="Q413" s="6" t="n">
-        <v>7.23</v>
+        <v>9.91</v>
       </c>
       <c r="R413" s="6" t="n"/>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 4.43, "vendor 9": 9.6, "vendor 11": 7.5, "vendor 13": 4.6, "vendor 14": 10}</t>
+          <t>{"vendor 6": 5.58, "vendor 9": 15.24, "vendor 11": 8, "vendor 13": 5.75, "vendor 14": 15}</t>
         </is>
       </c>
       <c r="T413" s="4" t="n"/>
       <c r="U413" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 200 ชิ้น | ราคาต่อหน่วย 4.43 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 4.43 สูงสุด 10 บาท</t>
+          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 99 ชิ้น | ราคาต่อหน่วย 5.58 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 5.58 สูงสุด 15.24 บาท</t>
         </is>
       </c>
     </row>
@@ -33031,17 +33011,17 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>201 - 500</t>
+          <t>100 - 200</t>
         </is>
       </c>
       <c r="J414" s="5" t="n">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="K414" s="5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L414" s="6" t="n">
-        <v>3.28</v>
+        <v>4.43</v>
       </c>
       <c r="M414" t="inlineStr">
         <is>
@@ -33052,24 +33032,24 @@
         <v>5</v>
       </c>
       <c r="O414" s="6" t="n">
-        <v>3.28</v>
+        <v>4.43</v>
       </c>
       <c r="P414" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q414" s="6" t="n">
-        <v>5.87</v>
+        <v>7.23</v>
       </c>
       <c r="R414" s="6" t="n"/>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 3.28, "vendor 9": 6.64, "vendor 11": 7, "vendor 13": 3.45, "vendor 14": 9}</t>
+          <t>{"vendor 6": 4.43, "vendor 9": 9.6, "vendor 11": 7.5, "vendor 13": 4.6, "vendor 14": 10}</t>
         </is>
       </c>
       <c r="T414" s="4" t="n"/>
       <c r="U414" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 3.28 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 3.28 สูงสุด 9 บาท</t>
+          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 200 ชิ้น | ราคาต่อหน่วย 4.43 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 4.43 สูงสุด 10 บาท</t>
         </is>
       </c>
     </row>
@@ -33112,17 +33092,17 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>201 - 500</t>
         </is>
       </c>
       <c r="J415" s="5" t="n">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="K415" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L415" s="6" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="M415" t="inlineStr">
         <is>
@@ -33133,31 +33113,31 @@
         <v>5</v>
       </c>
       <c r="O415" s="6" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="P415" s="6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q415" s="6" t="n">
-        <v>5.11</v>
+        <v>5.87</v>
       </c>
       <c r="R415" s="6" t="n"/>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 2.88, "vendor 9": 5.18, "vendor 11": 6, "vendor 13": 3, "vendor 14": 8.5}</t>
+          <t>{"vendor 6": 3.28, "vendor 9": 6.64, "vendor 11": 7, "vendor 13": 3.45, "vendor 14": 9}</t>
         </is>
       </c>
       <c r="T415" s="4" t="n"/>
       <c r="U415" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 2.88 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 2.88 สูงสุด 8.5 บาท</t>
+          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 3.28 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 3.28 สูงสุด 9 บาท</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>PrintRate-62</t>
+          <t>PrintRate-61</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -33172,12 +33152,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>shelf talker15x15 cm อาร์ตการ์ด300g</t>
+          <t>shelf stip 4x40 cm อาร์ตการ์ด300g</t>
         </is>
       </c>
       <c r="F416" s="4" t="inlineStr">
@@ -33186,52 +33166,52 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H416" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>1 - 50</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J416" s="5" t="n">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="K416" s="5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="L416" s="6" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>vendor 11</t>
+          <t>vendor 6</t>
         </is>
       </c>
       <c r="N416" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O416" s="6" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="P416" s="6" t="n">
-        <v>33.66</v>
+        <v>8.5</v>
       </c>
       <c r="Q416" s="6" t="n">
-        <v>20.63</v>
+        <v>5.11</v>
       </c>
       <c r="R416" s="6" t="n"/>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 17.25, "vendor 9": 33.66, "vendor 11": 10, "vendor 13": 17.25, "vendor 14": 25}</t>
+          <t>{"vendor 6": 2.88, "vendor 9": 5.18, "vendor 11": 6, "vendor 13": 3, "vendor 14": 8.5}</t>
         </is>
       </c>
       <c r="T416" s="4" t="n"/>
       <c r="U416" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 50 ชิ้น | ราคาต่อหน่วย 10 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 10 สูงสุด 33.66 บาท</t>
+          <t>[PrintRate-61] shelf stip 4x40 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 2.88 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 5 ราย ต่ำสุด 2.88 สูงสุด 8.5 บาท</t>
         </is>
       </c>
     </row>
@@ -33274,17 +33254,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>51 - 99</t>
+          <t>1 - 50</t>
         </is>
       </c>
       <c r="J417" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K417" s="5" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="L417" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M417" t="inlineStr">
         <is>
@@ -33295,24 +33275,24 @@
         <v>5</v>
       </c>
       <c r="O417" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P417" s="6" t="n">
-        <v>20</v>
+        <v>33.66</v>
       </c>
       <c r="Q417" s="6" t="n">
-        <v>13.14</v>
+        <v>20.63</v>
       </c>
       <c r="R417" s="6" t="n"/>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 9": 13.72, "vendor 11": 9, "vendor 13": 11.5, "vendor 14": 20}</t>
+          <t>{"vendor 6": 17.25, "vendor 9": 33.66, "vendor 11": 10, "vendor 13": 17.25, "vendor 14": 25}</t>
         </is>
       </c>
       <c r="T417" s="4" t="n"/>
       <c r="U417" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 99 ชิ้น | ราคาต่อหน่วย 9 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 9 สูงสุด 20 บาท</t>
+          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 50 ชิ้น | ราคาต่อหน่วย 10 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 10 สูงสุด 33.66 บาท</t>
         </is>
       </c>
     </row>
@@ -33355,17 +33335,17 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>100 - 200</t>
+          <t>51 - 99</t>
         </is>
       </c>
       <c r="J418" s="5" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="K418" s="5" t="n">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="L418" s="6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="M418" t="inlineStr">
         <is>
@@ -33376,24 +33356,24 @@
         <v>5</v>
       </c>
       <c r="O418" s="6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="P418" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q418" s="6" t="n">
-        <v>10.6</v>
+        <v>13.14</v>
       </c>
       <c r="R418" s="6" t="n"/>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 10.35, "vendor 9": 8.64, "vendor 11": 8.5, "vendor 13": 10.5, "vendor 14": 15}</t>
+          <t>{"vendor 6": 11.5, "vendor 9": 13.72, "vendor 11": 9, "vendor 13": 11.5, "vendor 14": 20}</t>
         </is>
       </c>
       <c r="T418" s="4" t="n"/>
       <c r="U418" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 200 ชิ้น | ราคาต่อหน่วย 8.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 8.5 สูงสุด 15 บาท</t>
+          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 99 ชิ้น | ราคาต่อหน่วย 9 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 9 สูงสุด 20 บาท</t>
         </is>
       </c>
     </row>
@@ -33436,45 +33416,45 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>201 - 500</t>
+          <t>100 - 200</t>
         </is>
       </c>
       <c r="J419" s="5" t="n">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="K419" s="5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L419" s="6" t="n">
-        <v>5.98</v>
+        <v>8.5</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 11</t>
         </is>
       </c>
       <c r="N419" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O419" s="6" t="n">
-        <v>5.98</v>
+        <v>8.5</v>
       </c>
       <c r="P419" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q419" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="R419" s="6" t="n"/>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 8.05, "vendor 9": 5.98, "vendor 11": 8, "vendor 13": 8.2, "vendor 14": 12}</t>
+          <t>{"vendor 6": 10.35, "vendor 9": 8.64, "vendor 11": 8.5, "vendor 13": 10.5, "vendor 14": 15}</t>
         </is>
       </c>
       <c r="T419" s="4" t="n"/>
       <c r="U419" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 5.98 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 5 ราย ต่ำสุด 5.98 สูงสุด 12 บาท</t>
+          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 200 ชิ้น | ราคาต่อหน่วย 8.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 5 ราย ต่ำสุด 8.5 สูงสุด 15 บาท</t>
         </is>
       </c>
     </row>
@@ -33517,17 +33497,17 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>201 - 500</t>
         </is>
       </c>
       <c r="J420" s="5" t="n">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="K420" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L420" s="6" t="n">
-        <v>4.66</v>
+        <v>5.98</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -33538,31 +33518,31 @@
         <v>5</v>
       </c>
       <c r="O420" s="6" t="n">
-        <v>4.66</v>
+        <v>5.98</v>
       </c>
       <c r="P420" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q420" s="6" t="n">
-        <v>6.7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R420" s="6" t="n"/>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 6.33, "vendor 9": 4.66, "vendor 11": 7, "vendor 13": 6.5, "vendor 14": 9}</t>
+          <t>{"vendor 6": 8.05, "vendor 9": 5.98, "vendor 11": 8, "vendor 13": 8.2, "vendor 14": 12}</t>
         </is>
       </c>
       <c r="T420" s="4" t="n"/>
       <c r="U420" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 4.66 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 5 ราย ต่ำสุด 4.66 สูงสุด 9 บาท</t>
+          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 5.98 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 5 ราย ต่ำสุด 5.98 สูงสุด 12 บาท</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>PrintRate-63</t>
+          <t>PrintRate-62</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -33577,19 +33557,38 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา</t>
-        </is>
-      </c>
-      <c r="F421" s="4" t="n"/>
-      <c r="J421" s="5" t="n"/>
-      <c r="K421" s="5" t="n"/>
+          <t>shelf talker15x15 cm อาร์ตการ์ด300g</t>
+        </is>
+      </c>
+      <c r="F421" s="4" t="inlineStr">
+        <is>
+          <t>พิมพ์4สี จำนวน 1หน้า เคลือบ PVC</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>15</v>
+      </c>
+      <c r="H421" t="n">
+        <v>15</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>501 - 1,000</t>
+        </is>
+      </c>
+      <c r="J421" s="5" t="n">
+        <v>501</v>
+      </c>
+      <c r="K421" s="5" t="n">
+        <v>1000</v>
+      </c>
       <c r="L421" s="6" t="n">
-        <v>140</v>
+        <v>4.66</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -33597,34 +33596,34 @@
         </is>
       </c>
       <c r="N421" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O421" s="6" t="n">
-        <v>140</v>
+        <v>4.66</v>
       </c>
       <c r="P421" s="6" t="n">
-        <v>450</v>
+        <v>9</v>
       </c>
       <c r="Q421" s="6" t="n">
-        <v>256.57</v>
+        <v>6.7</v>
       </c>
       <c r="R421" s="6" t="n"/>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 195.5, "vendor 9": 140, "vendor 10": 250, "vendor 11": 450, "vendor 13": 195.5, "vendor 14": 200, "vendor 15": 365}</t>
+          <t>{"vendor 6": 6.33, "vendor 9": 4.66, "vendor 11": 7, "vendor 13": 6.5, "vendor 14": 9}</t>
         </is>
       </c>
       <c r="T421" s="4" t="n"/>
       <c r="U421" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-63] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 140 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 140 สูงสุด 450 บาท</t>
+          <t>[PrintRate-62] shelf talker15x15 cm อาร์ตการ์ด300g | รายละเอียด: พิมพ์4สี จำนวน 1หน้า เคลือบ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 4.66 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 5 ราย ต่ำสุด 4.66 สูงสุด 9 บาท</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>PrintRate-64</t>
+          <t>PrintRate-63</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -33639,19 +33638,19 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F422" s="4" t="n"/>
       <c r="J422" s="5" t="n"/>
       <c r="K422" s="5" t="n"/>
       <c r="L422" s="6" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -33662,31 +33661,31 @@
         <v>7</v>
       </c>
       <c r="O422" s="6" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="P422" s="6" t="n">
-        <v>615</v>
+        <v>450</v>
       </c>
       <c r="Q422" s="6" t="n">
-        <v>332.71</v>
+        <v>256.57</v>
       </c>
       <c r="R422" s="6" t="n"/>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 207, "vendor 9": 180, "vendor 10": 300, "vendor 11": 600, "vendor 13": 207, "vendor 14": 220, "vendor 15": 615}</t>
+          <t>{"vendor 6": 195.5, "vendor 9": 140, "vendor 10": 250, "vendor 11": 450, "vendor 13": 195.5, "vendor 14": 200, "vendor 15": 365}</t>
         </is>
       </c>
       <c r="T422" s="4" t="n"/>
       <c r="U422" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-64] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 180 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 180 สูงสุด 615 บาท</t>
+          <t>[PrintRate-63] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 140 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 140 สูงสุด 450 บาท</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>PrintRate-65</t>
+          <t>PrintRate-64</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -33701,19 +33700,19 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ</t>
+          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F423" s="4" t="n"/>
       <c r="J423" s="5" t="n"/>
       <c r="K423" s="5" t="n"/>
       <c r="L423" s="6" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -33724,31 +33723,31 @@
         <v>7</v>
       </c>
       <c r="O423" s="6" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="P423" s="6" t="n">
-        <v>550</v>
+        <v>615</v>
       </c>
       <c r="Q423" s="6" t="n">
-        <v>284.75</v>
+        <v>332.71</v>
       </c>
       <c r="R423" s="6" t="n"/>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 201.25, "vendor 9": 145, "vendor 10": 250, "vendor 11": 550, "vendor 13": 202, "vendor 14": 210, "vendor 15": 435}</t>
+          <t>{"vendor 6": 207, "vendor 9": 180, "vendor 10": 300, "vendor 11": 600, "vendor 13": 207, "vendor 14": 220, "vendor 15": 615}</t>
         </is>
       </c>
       <c r="T423" s="4" t="n"/>
       <c r="U423" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-65] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 145 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 145 สูงสุด 550 บาท</t>
+          <t>[PrintRate-64] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 180 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 180 สูงสุด 615 บาท</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>PrintRate-66</t>
+          <t>PrintRate-65</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -33763,19 +33762,19 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ</t>
+          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F424" s="4" t="n"/>
       <c r="J424" s="5" t="n"/>
       <c r="K424" s="5" t="n"/>
       <c r="L424" s="6" t="n">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -33786,31 +33785,31 @@
         <v>7</v>
       </c>
       <c r="O424" s="6" t="n">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="P424" s="6" t="n">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="Q424" s="6" t="n">
-        <v>353.25</v>
+        <v>284.75</v>
       </c>
       <c r="R424" s="6" t="n"/>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 212.75, "vendor 9": 185, "vendor 10": 250, "vendor 11": 700, "vendor 13": 215, "vendor 14": 225, "vendor 15": 685}</t>
+          <t>{"vendor 6": 201.25, "vendor 9": 145, "vendor 10": 250, "vendor 11": 550, "vendor 13": 202, "vendor 14": 210, "vendor 15": 435}</t>
         </is>
       </c>
       <c r="T424" s="4" t="n"/>
       <c r="U424" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-66] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 185 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 185 สูงสุด 700 บาท</t>
+          <t>[PrintRate-65] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 145 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 145 สูงสุด 550 บาท</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>PrintRate-67</t>
+          <t>PrintRate-66</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -33825,19 +33824,19 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F425" s="4" t="n"/>
       <c r="J425" s="5" t="n"/>
       <c r="K425" s="5" t="n"/>
       <c r="L425" s="6" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -33845,34 +33844,34 @@
         </is>
       </c>
       <c r="N425" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O425" s="6" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="P425" s="6" t="n">
-        <v>530</v>
+        <v>700</v>
       </c>
       <c r="Q425" s="6" t="n">
-        <v>298.33</v>
+        <v>353.25</v>
       </c>
       <c r="R425" s="6" t="n"/>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 230, "vendor 9": 160, "vendor 10": 400, "vendor 11": 530, "vendor 13": 230, "vendor 14": 240}</t>
+          <t>{"vendor 6": 212.75, "vendor 9": 185, "vendor 10": 250, "vendor 11": 700, "vendor 13": 215, "vendor 14": 225, "vendor 15": 685}</t>
         </is>
       </c>
       <c r="T425" s="4" t="n"/>
       <c r="U425" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-67] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 160 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 160 สูงสุด 530 บาท</t>
+          <t>[PrintRate-66] PP Board 3 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 185 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 185 สูงสุด 700 บาท</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>PrintRate-68</t>
+          <t>PrintRate-67</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -33887,19 +33886,19 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F426" s="4" t="n"/>
       <c r="J426" s="5" t="n"/>
       <c r="K426" s="5" t="n"/>
       <c r="L426" s="6" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
@@ -33910,31 +33909,31 @@
         <v>6</v>
       </c>
       <c r="O426" s="6" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="P426" s="6" t="n">
-        <v>680</v>
+        <v>530</v>
       </c>
       <c r="Q426" s="6" t="n">
-        <v>347.67</v>
+        <v>298.33</v>
       </c>
       <c r="R426" s="6" t="n"/>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 253, "vendor 9": 200, "vendor 10": 450, "vendor 11": 680, "vendor 13": 253, "vendor 14": 250}</t>
+          <t>{"vendor 6": 230, "vendor 9": 160, "vendor 10": 400, "vendor 11": 530, "vendor 13": 230, "vendor 14": 240}</t>
         </is>
       </c>
       <c r="T426" s="4" t="n"/>
       <c r="U426" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-68] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 200 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 200 สูงสุด 680 บาท</t>
+          <t>[PrintRate-67] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 160 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 160 สูงสุด 530 บาท</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>PrintRate-69</t>
+          <t>PrintRate-68</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -33949,19 +33948,19 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ</t>
+          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F427" s="4" t="n"/>
       <c r="J427" s="5" t="n"/>
       <c r="K427" s="5" t="n"/>
       <c r="L427" s="6" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -33972,31 +33971,31 @@
         <v>6</v>
       </c>
       <c r="O427" s="6" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="P427" s="6" t="n">
-        <v>580</v>
+        <v>680</v>
       </c>
       <c r="Q427" s="6" t="n">
-        <v>311.08</v>
+        <v>347.67</v>
       </c>
       <c r="R427" s="6" t="n"/>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 235.75, "vendor 9": 165, "vendor 10": 400, "vendor 11": 580, "vendor 13": 235.75, "vendor 14": 250}</t>
+          <t>{"vendor 6": 253, "vendor 9": 200, "vendor 10": 450, "vendor 11": 680, "vendor 13": 253, "vendor 14": 250}</t>
         </is>
       </c>
       <c r="T427" s="4" t="n"/>
       <c r="U427" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-69] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 165 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 165 สูงสุด 580 บาท</t>
+          <t>[PrintRate-68] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 200 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 200 สูงสุด 680 บาท</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>PrintRate-70</t>
+          <t>PrintRate-69</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -34011,19 +34010,19 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ</t>
+          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F428" s="4" t="n"/>
       <c r="J428" s="5" t="n"/>
       <c r="K428" s="5" t="n"/>
       <c r="L428" s="6" t="n">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -34034,31 +34033,31 @@
         <v>6</v>
       </c>
       <c r="O428" s="6" t="n">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="P428" s="6" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="Q428" s="6" t="n">
-        <v>355.62</v>
+        <v>311.08</v>
       </c>
       <c r="R428" s="6" t="n"/>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 258.75, "vendor 9": 205, "vendor 10": 450, "vendor 11": 700, "vendor 13": 260, "vendor 14": 260}</t>
+          <t>{"vendor 6": 235.75, "vendor 9": 165, "vendor 10": 400, "vendor 11": 580, "vendor 13": 235.75, "vendor 14": 250}</t>
         </is>
       </c>
       <c r="T428" s="4" t="n"/>
       <c r="U428" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-70] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 205 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 205 สูงสุด 700 บาท</t>
+          <t>[PrintRate-69] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 165 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 165 สูงสุด 580 บาท</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>PrintRate-71</t>
+          <t>PrintRate-70</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -34073,19 +34072,19 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F429" s="4" t="n"/>
       <c r="J429" s="5" t="n"/>
       <c r="K429" s="5" t="n"/>
       <c r="L429" s="6" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="M429" t="inlineStr">
         <is>
@@ -34093,34 +34092,34 @@
         </is>
       </c>
       <c r="N429" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O429" s="6" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="P429" s="6" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="Q429" s="6" t="n">
-        <v>336.75</v>
+        <v>355.62</v>
       </c>
       <c r="R429" s="6" t="n"/>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 270.25, "vendor 9": 180, "vendor 10": 400, "vendor 11": 550, "vendor 13": 272, "vendor 14": 280, "vendor 15": 405}</t>
+          <t>{"vendor 6": 258.75, "vendor 9": 205, "vendor 10": 450, "vendor 11": 700, "vendor 13": 260, "vendor 14": 260}</t>
         </is>
       </c>
       <c r="T429" s="4" t="n"/>
       <c r="U429" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-71] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 180 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 180 สูงสุด 550 บาท</t>
+          <t>[PrintRate-70] PP Board 4 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 205 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 205 สูงสุด 700 บาท</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>PrintRate-72</t>
+          <t>PrintRate-71</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -34135,19 +34134,19 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F430" s="4" t="n"/>
       <c r="J430" s="5" t="n"/>
       <c r="K430" s="5" t="n"/>
       <c r="L430" s="6" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="M430" t="inlineStr">
         <is>
@@ -34158,31 +34157,31 @@
         <v>7</v>
       </c>
       <c r="O430" s="6" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="P430" s="6" t="n">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="Q430" s="6" t="n">
-        <v>409.57</v>
+        <v>336.75</v>
       </c>
       <c r="R430" s="6" t="n"/>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 276, "vendor 9": 220, "vendor 10": 450, "vendor 11": 700, "vendor 13": 276, "vendor 14": 290, "vendor 15": 655}</t>
+          <t>{"vendor 6": 270.25, "vendor 9": 180, "vendor 10": 400, "vendor 11": 550, "vendor 13": 272, "vendor 14": 280, "vendor 15": 405}</t>
         </is>
       </c>
       <c r="T430" s="4" t="n"/>
       <c r="U430" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-72] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 220 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 220 สูงสุด 700 บาท</t>
+          <t>[PrintRate-71] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 180 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 180 สูงสุด 550 บาท</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>PrintRate-73</t>
+          <t>PrintRate-72</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -34197,19 +34196,19 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ</t>
+          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F431" s="4" t="n"/>
       <c r="J431" s="5" t="n"/>
       <c r="K431" s="5" t="n"/>
       <c r="L431" s="6" t="n">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="M431" t="inlineStr">
         <is>
@@ -34220,31 +34219,31 @@
         <v>7</v>
       </c>
       <c r="O431" s="6" t="n">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="P431" s="6" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q431" s="6" t="n">
-        <v>361.71</v>
+        <v>409.57</v>
       </c>
       <c r="R431" s="6" t="n"/>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 276, "vendor 9": 185, "vendor 10": 400, "vendor 11": 600, "vendor 13": 276, "vendor 14": 290, "vendor 15": 505}</t>
+          <t>{"vendor 6": 276, "vendor 9": 220, "vendor 10": 450, "vendor 11": 700, "vendor 13": 276, "vendor 14": 290, "vendor 15": 655}</t>
         </is>
       </c>
       <c r="T431" s="4" t="n"/>
       <c r="U431" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-73] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 185 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 185 สูงสุด 600 บาท</t>
+          <t>[PrintRate-72] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 220 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 220 สูงสุด 700 บาท</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>PrintRate-74</t>
+          <t>PrintRate-73</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -34259,19 +34258,19 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ</t>
+          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F432" s="4" t="n"/>
       <c r="J432" s="5" t="n"/>
       <c r="K432" s="5" t="n"/>
       <c r="L432" s="6" t="n">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -34282,31 +34281,31 @@
         <v>7</v>
       </c>
       <c r="O432" s="6" t="n">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="P432" s="6" t="n">
-        <v>725</v>
+        <v>600</v>
       </c>
       <c r="Q432" s="6" t="n">
-        <v>423.39</v>
+        <v>361.71</v>
       </c>
       <c r="R432" s="6" t="n"/>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 281.75, "vendor 9": 225, "vendor 10": 450, "vendor 11": 700, "vendor 13": 282, "vendor 14": 300, "vendor 15": 725}</t>
+          <t>{"vendor 6": 276, "vendor 9": 185, "vendor 10": 400, "vendor 11": 600, "vendor 13": 276, "vendor 14": 290, "vendor 15": 505}</t>
         </is>
       </c>
       <c r="T432" s="4" t="n"/>
       <c r="U432" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-74] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 225 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 225 สูงสุด 725 บาท</t>
+          <t>[PrintRate-73] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นธรรมดา -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 185 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 185 สูงสุด 600 บาท</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>PrintRate-75</t>
+          <t>PrintRate-74</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -34321,19 +34320,19 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F433" s="4" t="n"/>
       <c r="J433" s="5" t="n"/>
       <c r="K433" s="5" t="n"/>
       <c r="L433" s="6" t="n">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -34344,31 +34343,31 @@
         <v>7</v>
       </c>
       <c r="O433" s="6" t="n">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="P433" s="6" t="n">
-        <v>520</v>
+        <v>725</v>
       </c>
       <c r="Q433" s="6" t="n">
-        <v>283.89</v>
+        <v>423.39</v>
       </c>
       <c r="R433" s="6" t="n"/>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 247.25, "vendor 9": 120, "vendor 10": 250, "vendor 11": 350, "vendor 13": 250, "vendor 14": 250, "vendor 15": 520}</t>
+          <t>{"vendor 6": 281.75, "vendor 9": 225, "vendor 10": 450, "vendor 11": 700, "vendor 13": 282, "vendor 14": 300, "vendor 15": 725}</t>
         </is>
       </c>
       <c r="T433" s="4" t="n"/>
       <c r="U433" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-75] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-74] PP Board 5 มิล ติดสติกเกอร์ PVC ปริ้นกัน UV -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 225 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 225 สูงสุด 725 บาท</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>PrintRate-76</t>
+          <t>PrintRate-75</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -34383,12 +34382,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F434" s="4" t="n"/>
@@ -34423,14 +34422,14 @@
       <c r="T434" s="4" t="n"/>
       <c r="U434" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-76] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-75] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PrintRate-77</t>
+          <t>PrintRate-76</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -34445,12 +34444,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F435" s="4" t="n"/>
@@ -34485,14 +34484,14 @@
       <c r="T435" s="4" t="n"/>
       <c r="U435" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-77] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-76] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>PrintRate-78</t>
+          <t>PrintRate-77</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -34507,12 +34506,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F436" s="4" t="n"/>
@@ -34547,14 +34546,14 @@
       <c r="T436" s="4" t="n"/>
       <c r="U436" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-78] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-77] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>PrintRate-79</t>
+          <t>PrintRate-78</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -34569,19 +34568,19 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F437" s="4" t="n"/>
       <c r="J437" s="5" t="n"/>
       <c r="K437" s="5" t="n"/>
       <c r="L437" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="M437" t="inlineStr">
         <is>
@@ -34592,31 +34591,31 @@
         <v>7</v>
       </c>
       <c r="O437" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="P437" s="6" t="n">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="Q437" s="6" t="n">
-        <v>303.71</v>
+        <v>283.89</v>
       </c>
       <c r="R437" s="6" t="n"/>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 253, "vendor 9": 125, "vendor 10": 250, "vendor 11": 400, "vendor 13": 253, "vendor 14": 255, "vendor 15": 590}</t>
+          <t>{"vendor 6": 247.25, "vendor 9": 120, "vendor 10": 250, "vendor 11": 350, "vendor 13": 250, "vendor 14": 250, "vendor 15": 520}</t>
         </is>
       </c>
       <c r="T437" s="4" t="n"/>
       <c r="U437" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-79] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-78] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>PrintRate-80</t>
+          <t>PrintRate-79</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -34631,12 +34630,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F438" s="4" t="n"/>
@@ -34671,14 +34670,14 @@
       <c r="T438" s="4" t="n"/>
       <c r="U438" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-80] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-79] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>PrintRate-81</t>
+          <t>PrintRate-80</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -34693,12 +34692,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F439" s="4" t="n"/>
@@ -34733,14 +34732,14 @@
       <c r="T439" s="4" t="n"/>
       <c r="U439" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-81] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-80] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>PrintRate-82</t>
+          <t>PrintRate-81</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -34755,12 +34754,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F440" s="4" t="n"/>
@@ -34795,14 +34794,14 @@
       <c r="T440" s="4" t="n"/>
       <c r="U440" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-82] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-81] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>PrintRate-83</t>
+          <t>PrintRate-82</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -34817,19 +34816,19 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F441" s="4" t="n"/>
       <c r="J441" s="5" t="n"/>
       <c r="K441" s="5" t="n"/>
       <c r="L441" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="M441" t="inlineStr">
         <is>
@@ -34840,31 +34839,31 @@
         <v>7</v>
       </c>
       <c r="O441" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P441" s="6" t="n">
-        <v>520</v>
+        <v>590</v>
       </c>
       <c r="Q441" s="6" t="n">
-        <v>294.21</v>
+        <v>303.71</v>
       </c>
       <c r="R441" s="6" t="n"/>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 264.5, "vendor 9": 120, "vendor 10": 250, "vendor 11": 400, "vendor 13": 265, "vendor 14": 240, "vendor 15": 520}</t>
+          <t>{"vendor 6": 253, "vendor 9": 125, "vendor 10": 250, "vendor 11": 400, "vendor 13": 253, "vendor 14": 255, "vendor 15": 590}</t>
         </is>
       </c>
       <c r="T441" s="4" t="n"/>
       <c r="U441" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-83] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-82] สติ๊กเกอร์ PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>PrintRate-84</t>
+          <t>PrintRate-83</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -34879,12 +34878,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F442" s="4" t="n"/>
@@ -34919,14 +34918,14 @@
       <c r="T442" s="4" t="n"/>
       <c r="U442" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-84] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-83] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>PrintRate-85</t>
+          <t>PrintRate-84</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -34941,12 +34940,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F443" s="4" t="n"/>
@@ -34981,14 +34980,14 @@
       <c r="T443" s="4" t="n"/>
       <c r="U443" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-85] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-84] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>PrintRate-86</t>
+          <t>PrintRate-85</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -35003,12 +35002,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F444" s="4" t="n"/>
@@ -35043,14 +35042,14 @@
       <c r="T444" s="4" t="n"/>
       <c r="U444" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-86] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
+          <t>[PrintRate-85] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>PrintRate-87</t>
+          <t>PrintRate-86</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -35065,19 +35064,19 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา</t>
         </is>
       </c>
       <c r="F445" s="4" t="n"/>
       <c r="J445" s="5" t="n"/>
       <c r="K445" s="5" t="n"/>
       <c r="L445" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
@@ -35088,31 +35087,31 @@
         <v>7</v>
       </c>
       <c r="O445" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="P445" s="6" t="n">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="Q445" s="6" t="n">
-        <v>315.18</v>
+        <v>294.21</v>
       </c>
       <c r="R445" s="6" t="n"/>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 270.25, "vendor 9": 125, "vendor 10": 250, "vendor 11": 450, "vendor 13": 271, "vendor 14": 250, "vendor 15": 590}</t>
+          <t>{"vendor 6": 264.5, "vendor 9": 120, "vendor 10": 250, "vendor 11": 400, "vendor 13": 265, "vendor 14": 240, "vendor 15": 520}</t>
         </is>
       </c>
       <c r="T445" s="4" t="n"/>
       <c r="U445" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-87] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-86] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ตัดสี่เหลี่ยมธรรมดา | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 120 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 120 สูงสุด 520 บาท</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>PrintRate-88</t>
+          <t>PrintRate-87</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -35127,12 +35126,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F446" s="4" t="n"/>
@@ -35167,14 +35166,14 @@
       <c r="T446" s="4" t="n"/>
       <c r="U446" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-88] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-87] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 1 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PrintRate-89</t>
+          <t>PrintRate-88</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -35189,12 +35188,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F447" s="4" t="n"/>
@@ -35229,14 +35228,14 @@
       <c r="T447" s="4" t="n"/>
       <c r="U447" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-89] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-88] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 2 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>PrintRate-90</t>
+          <t>PrintRate-89</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -35251,12 +35250,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F448" s="4" t="n"/>
@@ -35291,14 +35290,14 @@
       <c r="T448" s="4" t="n"/>
       <c r="U448" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-90] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
+          <t>[PrintRate-89] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 3 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>PrintRate-90.1</t>
+          <t>PrintRate-90</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -35318,49 +35317,49 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>ราคาค่าเคลือบลามิเนต</t>
+          <t>สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ</t>
         </is>
       </c>
       <c r="F449" s="4" t="n"/>
       <c r="J449" s="5" t="n"/>
       <c r="K449" s="5" t="n"/>
       <c r="L449" s="6" t="n">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N449" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O449" s="6" t="n">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="P449" s="6" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="Q449" s="6" t="n">
-        <v>184.09</v>
+        <v>315.18</v>
       </c>
       <c r="R449" s="6" t="n"/>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 302.45, "vendor 10": 50, "vendor 11": 500, "vendor 13": 33, "vendor 14": 35}</t>
+          <t>{"vendor 6": 270.25, "vendor 9": 125, "vendor 10": 250, "vendor 11": 450, "vendor 13": 271, "vendor 14": 250, "vendor 15": 590}</t>
         </is>
       </c>
       <c r="T449" s="4" t="n"/>
       <c r="U449" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-90.1] ราคาค่าเคลือบลามิเนต | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 33 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ | มีผู้เสนอราคา 5 ราย ต่ำสุด 33 สูงสุด 500 บาท</t>
+          <t>[PrintRate-90] สติ๊กเกอร์ใส PVC พิมพ์ละเอียด กัน UV พิมพ์ 4 สี -ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 125 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 125 สูงสุด 590 บาท</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>PrintRate-90.2</t>
+          <t>PrintRate-90.1</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -35380,44 +35379,48 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>ราคาค่าเคลือบด้าน</t>
+          <t>ราคาค่าเคลือบลามิเนต</t>
         </is>
       </c>
       <c r="F450" s="4" t="n"/>
       <c r="J450" s="5" t="n"/>
       <c r="K450" s="5" t="n"/>
       <c r="L450" s="6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N450" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O450" s="6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="P450" s="6" t="n">
         <v>500</v>
       </c>
       <c r="Q450" s="6" t="n">
-        <v>157.58</v>
+        <v>184.09</v>
       </c>
       <c r="R450" s="6" t="n"/>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 302.45, "vendor 9": 25, "vendor 10": 50, "vendor 11": 500, "vendor 13": 33, "vendor 14": 35}</t>
-        </is>
-      </c>
-      <c r="T450" s="4" t="n"/>
+          <t>{"vendor 6": 302.45, "vendor 10": 50, "vendor 11": 500, "vendor 13": 33, "vendor 14": 35}</t>
+        </is>
+      </c>
+      <c r="T450" s="4" t="inlineStr">
+        <is>
+          <t>พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
+        </is>
+      </c>
       <c r="U450" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-90.2] ราคาค่าเคลือบด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 25 บาท (ยังไม่รวม VAT 7%) | มีผู้เสนอราคา 6 ราย ต่ำสุด 25 สูงสุด 500 บาท</t>
+          <t>[PrintRate-90.1] ราคาค่าเคลือบลามิเนต | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 33 บาท (ยังไม่รวม VAT 7%) | มีผู้เสนอราคา 5 ราย ต่ำสุด 33 สูงสุด 500 บาท | หมายเหตุ: พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>PrintRate-90.3</t>
+          <t>PrintRate-90.2</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -35437,7 +35440,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>ราคาค่าเคลือบมัน</t>
+          <t>ราคาค่าเคลือบด้าน</t>
         </is>
       </c>
       <c r="F451" s="4" t="n"/>
@@ -35464,17 +35467,21 @@
           <t>{"vendor 6": 302.45, "vendor 9": 25, "vendor 10": 50, "vendor 11": 500, "vendor 13": 33, "vendor 14": 35}</t>
         </is>
       </c>
-      <c r="T451" s="4" t="n"/>
+      <c r="T451" s="4" t="inlineStr">
+        <is>
+          <t>พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
+        </is>
+      </c>
       <c r="U451" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-90.3] ราคาค่าเคลือบมัน | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 25 บาท (ยังไม่รวม VAT 7%) | มีผู้เสนอราคา 6 ราย ต่ำสุด 25 สูงสุด 500 บาท</t>
+          <t>[PrintRate-90.2] ราคาค่าเคลือบด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 25 บาท (ยังไม่รวม VAT 7%) | มีผู้เสนอราคา 6 ราย ต่ำสุด 25 สูงสุด 500 บาท | หมายเหตุ: พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>PrintRate-91</t>
+          <t>PrintRate-90.3</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -35489,62 +35496,46 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Sticker Remover 8 x 10 cm.</t>
+          <t>ราคาค่าเคลือบมัน</t>
         </is>
       </c>
       <c r="F452" s="4" t="n"/>
-      <c r="G452" t="n">
-        <v>8</v>
-      </c>
-      <c r="H452" t="n">
-        <v>10</v>
-      </c>
-      <c r="I452" t="inlineStr">
-        <is>
-          <t>1 - 500</t>
-        </is>
-      </c>
-      <c r="J452" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K452" s="5" t="n">
+      <c r="J452" s="5" t="n"/>
+      <c r="K452" s="5" t="n"/>
+      <c r="L452" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="N452" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O452" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="P452" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="L452" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>vendor 11</t>
-        </is>
-      </c>
-      <c r="N452" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="O452" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P452" s="6" t="n">
-        <v>15</v>
-      </c>
       <c r="Q452" s="6" t="n">
-        <v>6.01</v>
+        <v>157.58</v>
       </c>
       <c r="R452" s="6" t="n"/>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 5.75, "vendor 8": 5, "vendor 9": 4.85, "vendor 10": 3, "vendor 11": 2.5, "vendor 13": 6, "vendor 14": 15}</t>
-        </is>
-      </c>
-      <c r="T452" s="4" t="n"/>
+          <t>{"vendor 6": 302.45, "vendor 9": 25, "vendor 10": 50, "vendor 11": 500, "vendor 13": 33, "vendor 14": 35}</t>
+        </is>
+      </c>
+      <c r="T452" s="4" t="inlineStr">
+        <is>
+          <t>พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
+        </is>
+      </c>
       <c r="U452" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-91] Sticker Remover 8 x 10 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 500 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 7 ราย ต่ำสุด 2.5 สูงสุด 15 บาท</t>
+          <t>[PrintRate-90.3] ราคาค่าเคลือบมัน | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 25 บาท (ยังไม่รวม VAT 7%) | มีผู้เสนอราคา 6 ราย ต่ำสุด 25 สูงสุด 500 บาท | หมายเหตุ: พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
         </is>
       </c>
     </row>
@@ -35583,52 +35574,52 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>1 - 500</t>
         </is>
       </c>
       <c r="J453" s="5" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="K453" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L453" s="6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>vendor 10</t>
+          <t>vendor 11</t>
         </is>
       </c>
       <c r="N453" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O453" s="6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P453" s="6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q453" s="6" t="n">
-        <v>3.99</v>
+        <v>6.01</v>
       </c>
       <c r="R453" s="6" t="n"/>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 5": 2.7, "vendor 6": 4.6, "vendor 8": 2.5, "vendor 9": 3.94, "vendor 10": 2, "vendor 11": 2.2, "vendor 13": 5, "vendor 14": 9}</t>
+          <t>{"vendor 6": 5.75, "vendor 8": 5, "vendor 9": 4.85, "vendor 10": 3, "vendor 11": 2.5, "vendor 13": 6, "vendor 14": 15}</t>
         </is>
       </c>
       <c r="T453" s="4" t="n"/>
       <c r="U453" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-91] Sticker Remover 8 x 10 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 8 ราย ต่ำสุด 2 สูงสุด 9 บาท</t>
+          <t>[PrintRate-91] Sticker Remover 8 x 10 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 500 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 7 ราย ต่ำสุด 2.5 สูงสุด 15 บาท</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>PrintRate-92</t>
+          <t>PrintRate-91</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -35643,60 +35634,62 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Sticker PVC กัน UV ขนาดไม่เกิน A4</t>
+          <t>Sticker Remover 8 x 10 cm.</t>
         </is>
       </c>
       <c r="F454" s="4" t="n"/>
+      <c r="G454" t="n">
+        <v>8</v>
+      </c>
+      <c r="H454" t="n">
+        <v>10</v>
+      </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>1 - 100</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J454" s="5" t="n">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="K454" s="5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L454" s="6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>vendor 15</t>
+          <t>vendor 10</t>
         </is>
       </c>
       <c r="N454" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O454" s="6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P454" s="6" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="Q454" s="6" t="n">
-        <v>24.5</v>
+        <v>3.99</v>
       </c>
       <c r="R454" s="6" t="n"/>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 23, "vendor 8": 20, "vendor 9": 25.5, "vendor 10": 20, "vendor 11": 25, "vendor 13": 23, "vendor 14": 35}</t>
-        </is>
-      </c>
-      <c r="T454" s="4" t="inlineStr">
-        <is>
-          <t>/ | vendor 15/</t>
-        </is>
-      </c>
+          <t>{"vendor 5": 2.7, "vendor 6": 4.6, "vendor 8": 2.5, "vendor 9": 3.94, "vendor 10": 2, "vendor 11": 2.2, "vendor 13": 5, "vendor 14": 9}</t>
+        </is>
+      </c>
+      <c r="T454" s="4" t="n"/>
       <c r="U454" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 100 ชิ้น | ราคาต่อหน่วย 20 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 15 | มีผู้เสนอราคา 7 ราย ต่ำสุด 20 สูงสุด 35 บาท | หมายเหตุ: / | vendor 15/</t>
+          <t>[PrintRate-91] Sticker Remover 8 x 10 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 8 ราย ต่ำสุด 2 สูงสุด 9 บาท</t>
         </is>
       </c>
     </row>
@@ -35726,52 +35719,52 @@
           <t>Sticker PVC กัน UV ขนาดไม่เกิน A4</t>
         </is>
       </c>
-      <c r="F455" s="4" t="inlineStr">
-        <is>
-          <t>พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม</t>
-        </is>
-      </c>
+      <c r="F455" s="4" t="n"/>
       <c r="I455" t="inlineStr">
         <is>
-          <t>101 - 500</t>
+          <t>1 - 100</t>
         </is>
       </c>
       <c r="J455" s="5" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K455" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L455" s="6" t="n">
-        <v>19.55</v>
+        <v>20</v>
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>vendor 13</t>
+          <t>vendor 15</t>
         </is>
       </c>
       <c r="N455" s="5" t="n">
         <v>7</v>
       </c>
       <c r="O455" s="6" t="n">
-        <v>19.55</v>
+        <v>20</v>
       </c>
       <c r="P455" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q455" s="6" t="n">
-        <v>22.65</v>
+        <v>24.5</v>
       </c>
       <c r="R455" s="6" t="n"/>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 23, "vendor 8": 20, "vendor 9": 23, "vendor 10": 20, "vendor 11": 23, "vendor 13": 19.55, "vendor 14": 30}</t>
-        </is>
-      </c>
-      <c r="T455" s="4" t="n"/>
+          <t>{"vendor 6": 23, "vendor 8": 20, "vendor 9": 25.5, "vendor 10": 20, "vendor 11": 25, "vendor 13": 23, "vendor 14": 35}</t>
+        </is>
+      </c>
+      <c r="T455" s="4" t="inlineStr">
+        <is>
+          <t>/ | vendor 15/</t>
+        </is>
+      </c>
       <c r="U455" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 500 ชิ้น | ราคาต่อหน่วย 19.55 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 13 | มีผู้เสนอราคา 7 ราย ต่ำสุด 19.55 สูงสุด 30 บาท</t>
+          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 100 ชิ้น | ราคาต่อหน่วย 20 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 15 | มีผู้เสนอราคา 7 ราย ต่ำสุด 20 สูงสุด 35 บาท | หมายเหตุ: / | vendor 15/</t>
         </is>
       </c>
     </row>
@@ -35808,45 +35801,45 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>101 - 500</t>
         </is>
       </c>
       <c r="J456" s="5" t="n">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="K456" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L456" s="6" t="n">
-        <v>14.6</v>
+        <v>19.55</v>
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 13</t>
         </is>
       </c>
       <c r="N456" s="5" t="n">
         <v>7</v>
       </c>
       <c r="O456" s="6" t="n">
-        <v>14.6</v>
+        <v>19.55</v>
       </c>
       <c r="P456" s="6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q456" s="6" t="n">
-        <v>19.31</v>
+        <v>22.65</v>
       </c>
       <c r="R456" s="6" t="n"/>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 19.55, "vendor 8": 20, "vendor 9": 14.6, "vendor 10": 15, "vendor 11": 21, "vendor 13": 19, "vendor 14": 26}</t>
+          <t>{"vendor 6": 23, "vendor 8": 20, "vendor 9": 23, "vendor 10": 20, "vendor 11": 23, "vendor 13": 19.55, "vendor 14": 30}</t>
         </is>
       </c>
       <c r="T456" s="4" t="n"/>
       <c r="U456" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 14.6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 14.6 สูงสุด 26 บาท</t>
+          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 500 ชิ้น | ราคาต่อหน่วย 19.55 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 13 | มีผู้เสนอราคา 7 ราย ต่ำสุด 19.55 สูงสุด 30 บาท</t>
         </is>
       </c>
     </row>
@@ -35883,17 +35876,17 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>1,001 - 1,500</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J457" s="5" t="n">
-        <v>1001</v>
+        <v>501</v>
       </c>
       <c r="K457" s="5" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L457" s="6" t="n">
-        <v>11.45</v>
+        <v>14.6</v>
       </c>
       <c r="M457" t="inlineStr">
         <is>
@@ -35904,24 +35897,24 @@
         <v>7</v>
       </c>
       <c r="O457" s="6" t="n">
-        <v>11.45</v>
+        <v>14.6</v>
       </c>
       <c r="P457" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q457" s="6" t="n">
-        <v>16.98</v>
+        <v>19.31</v>
       </c>
       <c r="R457" s="6" t="n"/>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 18.4, "vendor 8": 15, "vendor 9": 11.45, "vendor 10": 12, "vendor 11": 20, "vendor 13": 18, "vendor 14": 24}</t>
+          <t>{"vendor 6": 19.55, "vendor 8": 20, "vendor 9": 14.6, "vendor 10": 15, "vendor 11": 21, "vendor 13": 19, "vendor 14": 26}</t>
         </is>
       </c>
       <c r="T457" s="4" t="n"/>
       <c r="U457" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 11.45 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 11.45 สูงสุด 24 บาท</t>
+          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 14.6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 14.6 สูงสุด 26 บาท</t>
         </is>
       </c>
     </row>
@@ -35958,17 +35951,17 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>1,501 - 2,000</t>
+          <t>1,001 - 1,500</t>
         </is>
       </c>
       <c r="J458" s="5" t="n">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="K458" s="5" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="L458" s="6" t="n">
-        <v>9.68</v>
+        <v>11.45</v>
       </c>
       <c r="M458" t="inlineStr">
         <is>
@@ -35979,31 +35972,31 @@
         <v>7</v>
       </c>
       <c r="O458" s="6" t="n">
-        <v>9.68</v>
+        <v>11.45</v>
       </c>
       <c r="P458" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q458" s="6" t="n">
-        <v>15.85</v>
+        <v>16.98</v>
       </c>
       <c r="R458" s="6" t="n"/>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 17.25, "vendor 8": 15, "vendor 9": 9.68, "vendor 10": 12, "vendor 11": 18, "vendor 13": 17, "vendor 14": 22}</t>
+          <t>{"vendor 6": 18.4, "vendor 8": 15, "vendor 9": 11.45, "vendor 10": 12, "vendor 11": 20, "vendor 13": 18, "vendor 14": 24}</t>
         </is>
       </c>
       <c r="T458" s="4" t="n"/>
       <c r="U458" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,501 - 2,000 ชิ้น | ราคาต่อหน่วย 9.68 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 9.68 สูงสุด 22 บาท</t>
+          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 11.45 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 11.45 สูงสุด 24 บาท</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>PrintRate-93</t>
+          <t>PrintRate-92</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -36018,56 +36011,60 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Sticker PVC กัน UV ขนาดไม่เกิน A5</t>
-        </is>
-      </c>
-      <c r="F459" s="4" t="n"/>
+          <t>Sticker PVC กัน UV ขนาดไม่เกิน A4</t>
+        </is>
+      </c>
+      <c r="F459" s="4" t="inlineStr">
+        <is>
+          <t>พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม</t>
+        </is>
+      </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>1 - 100</t>
+          <t>1,501 - 2,000</t>
         </is>
       </c>
       <c r="J459" s="5" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="K459" s="5" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="L459" s="6" t="n">
-        <v>8</v>
+        <v>9.68</v>
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>vendor 10</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N459" s="5" t="n">
         <v>7</v>
       </c>
       <c r="O459" s="6" t="n">
-        <v>8</v>
+        <v>9.68</v>
       </c>
       <c r="P459" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q459" s="6" t="n">
-        <v>14.53</v>
+        <v>15.85</v>
       </c>
       <c r="R459" s="6" t="n"/>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 12.65, "vendor 8": 15, "vendor 9": 15.94, "vendor 10": 8, "vendor 11": 12.5, "vendor 13": 12.65, "vendor 14": 25}</t>
+          <t>{"vendor 6": 17.25, "vendor 8": 15, "vendor 9": 9.68, "vendor 10": 12, "vendor 11": 18, "vendor 13": 17, "vendor 14": 22}</t>
         </is>
       </c>
       <c r="T459" s="4" t="n"/>
       <c r="U459" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 100 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 8 สูงสุด 25 บาท</t>
+          <t>[PrintRate-92] Sticker PVC กัน UV ขนาดไม่เกิน A4 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,501 - 2,000 ชิ้น | ราคาต่อหน่วย 9.68 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 9.68 สูงสุด 22 บาท</t>
         </is>
       </c>
     </row>
@@ -36097,21 +36094,17 @@
           <t>Sticker PVC กัน UV ขนาดไม่เกิน A5</t>
         </is>
       </c>
-      <c r="F460" s="4" t="inlineStr">
-        <is>
-          <t>พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม</t>
-        </is>
-      </c>
+      <c r="F460" s="4" t="n"/>
       <c r="I460" t="inlineStr">
         <is>
-          <t>101 - 500</t>
+          <t>1 - 100</t>
         </is>
       </c>
       <c r="J460" s="5" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K460" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L460" s="6" t="n">
         <v>8</v>
@@ -36128,21 +36121,21 @@
         <v>8</v>
       </c>
       <c r="P460" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q460" s="6" t="n">
-        <v>13.71</v>
+        <v>14.53</v>
       </c>
       <c r="R460" s="6" t="n"/>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 12.65, "vendor 8": 15, "vendor 9": 14.8, "vendor 10": 8, "vendor 11": 11.5, "vendor 13": 12, "vendor 14": 22}</t>
+          <t>{"vendor 6": 12.65, "vendor 8": 15, "vendor 9": 15.94, "vendor 10": 8, "vendor 11": 12.5, "vendor 13": 12.65, "vendor 14": 25}</t>
         </is>
       </c>
       <c r="T460" s="4" t="n"/>
       <c r="U460" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 500 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 8 สูงสุด 22 บาท</t>
+          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 100 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 8 สูงสุด 25 บาท</t>
         </is>
       </c>
     </row>
@@ -36179,17 +36172,17 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>101 - 500</t>
         </is>
       </c>
       <c r="J461" s="5" t="n">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="K461" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L461" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M461" t="inlineStr">
         <is>
@@ -36200,24 +36193,24 @@
         <v>7</v>
       </c>
       <c r="O461" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P461" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q461" s="6" t="n">
-        <v>12.27</v>
+        <v>13.71</v>
       </c>
       <c r="R461" s="6" t="n"/>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 12.65, "vendor 8": 15, "vendor 9": 10.24, "vendor 10": 6, "vendor 11": 10.5, "vendor 13": 11.5, "vendor 14": 20}</t>
+          <t>{"vendor 6": 12.65, "vendor 8": 15, "vendor 9": 14.8, "vendor 10": 8, "vendor 11": 11.5, "vendor 13": 12, "vendor 14": 22}</t>
         </is>
       </c>
       <c r="T461" s="4" t="n"/>
       <c r="U461" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 20 บาท</t>
+          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 500 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 8 สูงสุด 22 บาท</t>
         </is>
       </c>
     </row>
@@ -36254,14 +36247,14 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>1,001 - 1,500</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J462" s="5" t="n">
-        <v>1001</v>
+        <v>501</v>
       </c>
       <c r="K462" s="5" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L462" s="6" t="n">
         <v>6</v>
@@ -36278,21 +36271,21 @@
         <v>6</v>
       </c>
       <c r="P462" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q462" s="6" t="n">
-        <v>10.94</v>
+        <v>12.27</v>
       </c>
       <c r="R462" s="6" t="n"/>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 8": 10, "vendor 9": 9.58, "vendor 10": 6, "vendor 11": 10, "vendor 13": 11.5, "vendor 14": 18}</t>
+          <t>{"vendor 6": 12.65, "vendor 8": 15, "vendor 9": 10.24, "vendor 10": 6, "vendor 11": 10.5, "vendor 13": 11.5, "vendor 14": 20}</t>
         </is>
       </c>
       <c r="T462" s="4" t="n"/>
       <c r="U462" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 18 บาท</t>
+          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 20 บาท</t>
         </is>
       </c>
     </row>
@@ -36329,14 +36322,14 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>1,501 - 2,000</t>
+          <t>1,001 - 1,500</t>
         </is>
       </c>
       <c r="J463" s="5" t="n">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="K463" s="5" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="L463" s="6" t="n">
         <v>6</v>
@@ -36353,28 +36346,28 @@
         <v>6</v>
       </c>
       <c r="P463" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q463" s="6" t="n">
-        <v>9.81</v>
+        <v>10.94</v>
       </c>
       <c r="R463" s="6" t="n"/>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 10.35, "vendor 8": 10, "vendor 9": 7.82, "vendor 10": 6, "vendor 11": 9, "vendor 13": 10.5, "vendor 14": 15}</t>
+          <t>{"vendor 6": 11.5, "vendor 8": 10, "vendor 9": 9.58, "vendor 10": 6, "vendor 11": 10, "vendor 13": 11.5, "vendor 14": 18}</t>
         </is>
       </c>
       <c r="T463" s="4" t="n"/>
       <c r="U463" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,501 - 2,000 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 15 บาท</t>
+          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 18 บาท</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>PrintRate-94</t>
+          <t>PrintRate-93</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -36389,28 +36382,32 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Sticker PVC กัน UV ขนาดไม่เกิน A3</t>
-        </is>
-      </c>
-      <c r="F464" s="4" t="n"/>
+          <t>Sticker PVC กัน UV ขนาดไม่เกิน A5</t>
+        </is>
+      </c>
+      <c r="F464" s="4" t="inlineStr">
+        <is>
+          <t>พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม</t>
+        </is>
+      </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>1 - 100</t>
+          <t>1,501 - 2,000</t>
         </is>
       </c>
       <c r="J464" s="5" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="K464" s="5" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="L464" s="6" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M464" t="inlineStr">
         <is>
@@ -36421,24 +36418,24 @@
         <v>7</v>
       </c>
       <c r="O464" s="6" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="P464" s="6" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="Q464" s="6" t="n">
-        <v>41.06</v>
+        <v>9.81</v>
       </c>
       <c r="R464" s="6" t="n"/>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 46, "vendor 8": 30, "vendor 9": 36.4, "vendor 10": 24, "vendor 11": 50, "vendor 13": 46, "vendor 14": 55}</t>
+          <t>{"vendor 6": 10.35, "vendor 8": 10, "vendor 9": 7.82, "vendor 10": 6, "vendor 11": 9, "vendor 13": 10.5, "vendor 14": 15}</t>
         </is>
       </c>
       <c r="T464" s="4" t="n"/>
       <c r="U464" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 100 ชิ้น | ราคาต่อหน่วย 24 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 24 สูงสุด 55 บาท</t>
+          <t>[PrintRate-93] Sticker PVC กัน UV ขนาดไม่เกิน A5 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,501 - 2,000 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 15 บาท</t>
         </is>
       </c>
     </row>
@@ -36468,21 +36465,17 @@
           <t>Sticker PVC กัน UV ขนาดไม่เกิน A3</t>
         </is>
       </c>
-      <c r="F465" s="4" t="inlineStr">
-        <is>
-          <t>พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม</t>
-        </is>
-      </c>
+      <c r="F465" s="4" t="n"/>
       <c r="I465" t="inlineStr">
         <is>
-          <t>101 - 500</t>
+          <t>1 - 100</t>
         </is>
       </c>
       <c r="J465" s="5" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K465" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L465" s="6" t="n">
         <v>24</v>
@@ -36499,21 +36492,21 @@
         <v>24</v>
       </c>
       <c r="P465" s="6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q465" s="6" t="n">
-        <v>38.71</v>
+        <v>41.06</v>
       </c>
       <c r="R465" s="6" t="n"/>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 46, "vendor 8": 30, "vendor 9": 34, "vendor 10": 24, "vendor 11": 46, "vendor 13": 41, "vendor 14": 50}</t>
+          <t>{"vendor 6": 46, "vendor 8": 30, "vendor 9": 36.4, "vendor 10": 24, "vendor 11": 50, "vendor 13": 46, "vendor 14": 55}</t>
         </is>
       </c>
       <c r="T465" s="4" t="n"/>
       <c r="U465" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 500 ชิ้น | ราคาต่อหน่วย 24 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 24 สูงสุด 50 บาท</t>
+          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 100 ชิ้น | ราคาต่อหน่วย 24 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 24 สูงสุด 55 บาท</t>
         </is>
       </c>
     </row>
@@ -36550,45 +36543,45 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>101 - 500</t>
         </is>
       </c>
       <c r="J466" s="5" t="n">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="K466" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L466" s="6" t="n">
-        <v>19.22</v>
+        <v>24</v>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 10</t>
         </is>
       </c>
       <c r="N466" s="5" t="n">
         <v>7</v>
       </c>
       <c r="O466" s="6" t="n">
-        <v>19.22</v>
+        <v>24</v>
       </c>
       <c r="P466" s="6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q466" s="6" t="n">
-        <v>34.35</v>
+        <v>38.71</v>
       </c>
       <c r="R466" s="6" t="n"/>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 40.25, "vendor 8": 30, "vendor 9": 19.22, "vendor 10": 24, "vendor 11": 42, "vendor 13": 40, "vendor 14": 45}</t>
+          <t>{"vendor 6": 46, "vendor 8": 30, "vendor 9": 34, "vendor 10": 24, "vendor 11": 46, "vendor 13": 41, "vendor 14": 50}</t>
         </is>
       </c>
       <c r="T466" s="4" t="n"/>
       <c r="U466" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 19.22 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 19.22 สูงสุด 45 บาท</t>
+          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 500 ชิ้น | ราคาต่อหน่วย 24 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 24 สูงสุด 50 บาท</t>
         </is>
       </c>
     </row>
@@ -36625,17 +36618,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>1,001 - 1,500</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J467" s="5" t="n">
-        <v>1001</v>
+        <v>501</v>
       </c>
       <c r="K467" s="5" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L467" s="6" t="n">
-        <v>17.45</v>
+        <v>19.22</v>
       </c>
       <c r="M467" t="inlineStr">
         <is>
@@ -36646,24 +36639,24 @@
         <v>7</v>
       </c>
       <c r="O467" s="6" t="n">
-        <v>17.45</v>
+        <v>19.22</v>
       </c>
       <c r="P467" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q467" s="6" t="n">
-        <v>31.75</v>
+        <v>34.35</v>
       </c>
       <c r="R467" s="6" t="n"/>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 36.8, "vendor 8": 25, "vendor 9": 17.45, "vendor 10": 24, "vendor 11": 40, "vendor 13": 37, "vendor 14": 42}</t>
+          <t>{"vendor 6": 40.25, "vendor 8": 30, "vendor 9": 19.22, "vendor 10": 24, "vendor 11": 42, "vendor 13": 40, "vendor 14": 45}</t>
         </is>
       </c>
       <c r="T467" s="4" t="n"/>
       <c r="U467" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 17.45 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 17.45 สูงสุด 42 บาท</t>
+          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 19.22 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 19.22 สูงสุด 45 บาท</t>
         </is>
       </c>
     </row>
@@ -36700,17 +36693,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>1,501 - 2,000</t>
+          <t>1,001 - 1,500</t>
         </is>
       </c>
       <c r="J468" s="5" t="n">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="K468" s="5" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="L468" s="6" t="n">
-        <v>16.34</v>
+        <v>17.45</v>
       </c>
       <c r="M468" t="inlineStr">
         <is>
@@ -36721,31 +36714,31 @@
         <v>7</v>
       </c>
       <c r="O468" s="6" t="n">
-        <v>16.34</v>
+        <v>17.45</v>
       </c>
       <c r="P468" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q468" s="6" t="n">
-        <v>29.83</v>
+        <v>31.75</v>
       </c>
       <c r="R468" s="6" t="n"/>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 34.5, "vendor 8": 25, "vendor 9": 16.34, "vendor 10": 24, "vendor 11": 36, "vendor 13": 35, "vendor 14": 38}</t>
+          <t>{"vendor 6": 36.8, "vendor 8": 25, "vendor 9": 17.45, "vendor 10": 24, "vendor 11": 40, "vendor 13": 37, "vendor 14": 42}</t>
         </is>
       </c>
       <c r="T468" s="4" t="n"/>
       <c r="U468" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,501 - 2,000 ชิ้น | ราคาต่อหน่วย 16.34 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 16.34 สูงสุด 38 บาท</t>
+          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 1,500 ชิ้น | ราคาต่อหน่วย 17.45 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 17.45 สูงสุด 42 บาท</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>PrintRate-95</t>
+          <t>PrintRate-94</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -36760,56 +36753,60 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Sale kit A4 กระดาษอาร์ตมัน 230gขนาดA4 พิมพ์ 4สี 1หน้า</t>
-        </is>
-      </c>
-      <c r="F469" s="4" t="n"/>
+          <t>Sticker PVC กัน UV ขนาดไม่เกิน A3</t>
+        </is>
+      </c>
+      <c r="F469" s="4" t="inlineStr">
+        <is>
+          <t>พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม</t>
+        </is>
+      </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>น้อยกว่า 50</t>
+          <t>1,501 - 2,000</t>
         </is>
       </c>
       <c r="J469" s="5" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="K469" s="5" t="n">
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="L469" s="6" t="n">
-        <v>15</v>
+        <v>16.34</v>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>vendor 15</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N469" s="5" t="n">
         <v>7</v>
       </c>
       <c r="O469" s="6" t="n">
-        <v>15</v>
+        <v>16.34</v>
       </c>
       <c r="P469" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q469" s="6" t="n">
-        <v>21.44</v>
+        <v>29.83</v>
       </c>
       <c r="R469" s="6" t="n"/>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 17.25, "vendor 8": 18, "vendor 9": 27.6, "vendor 11": 20, "vendor 13": 17.25, "vendor 14": 35, "vendor 15": 15}</t>
+          <t>{"vendor 6": 34.5, "vendor 8": 25, "vendor 9": 16.34, "vendor 10": 24, "vendor 11": 36, "vendor 13": 35, "vendor 14": 38}</t>
         </is>
       </c>
       <c r="T469" s="4" t="n"/>
       <c r="U469" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-95] Sale kit A4 กระดาษอาร์ตมัน 230gขนาดA4 พิมพ์ 4สี 1หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน น้อยกว่า 50 ชิ้น | ราคาต่อหน่วย 15 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 15 | มีผู้เสนอราคา 7 ราย ต่ำสุด 15 สูงสุด 35 บาท</t>
+          <t>[PrintRate-94] Sticker PVC กัน UV ขนาดไม่เกิน A3 | รายละเอียด: พิมพ์ 4 สี 1 ด้าน ตัดเหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,501 - 2,000 ชิ้น | ราคาต่อหน่วย 16.34 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 16.34 สูงสุด 38 บาท</t>
         </is>
       </c>
     </row>
@@ -36842,52 +36839,52 @@
       <c r="F470" s="4" t="n"/>
       <c r="I470" t="inlineStr">
         <is>
-          <t>51 - 500</t>
+          <t>น้อยกว่า 50</t>
         </is>
       </c>
       <c r="J470" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K470" s="5" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="L470" s="6" t="n">
-        <v>10.35</v>
+        <v>15</v>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>vendor 6</t>
+          <t>vendor 15</t>
         </is>
       </c>
       <c r="N470" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O470" s="6" t="n">
-        <v>10.35</v>
+        <v>15</v>
       </c>
       <c r="P470" s="6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q470" s="6" t="n">
-        <v>15.88</v>
+        <v>21.44</v>
       </c>
       <c r="R470" s="6" t="n"/>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 10.35, "vendor 8": 18, "vendor 9": 18.9, "vendor 11": 17.5, "vendor 13": 10.5, "vendor 14": 20}</t>
+          <t>{"vendor 6": 17.25, "vendor 8": 18, "vendor 9": 27.6, "vendor 11": 20, "vendor 13": 17.25, "vendor 14": 35, "vendor 15": 15}</t>
         </is>
       </c>
       <c r="T470" s="4" t="n"/>
       <c r="U470" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-95] Sale kit A4 กระดาษอาร์ตมัน 230gขนาดA4 พิมพ์ 4สี 1หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 500 ชิ้น | ราคาต่อหน่วย 10.35 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 6 ราย ต่ำสุด 10.35 สูงสุด 20 บาท</t>
+          <t>[PrintRate-95] Sale kit A4 กระดาษอาร์ตมัน 230gขนาดA4 พิมพ์ 4สี 1หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน น้อยกว่า 50 ชิ้น | ราคาต่อหน่วย 15 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 15 | มีผู้เสนอราคา 7 ราย ต่ำสุด 15 สูงสุด 35 บาท</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>PrintRate-96</t>
+          <t>PrintRate-95</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -36902,66 +36899,56 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Couponขนาด 8x7 cm (50ใบ/เล่ม)</t>
-        </is>
-      </c>
-      <c r="F471" s="4" t="inlineStr">
-        <is>
-          <t>กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม</t>
-        </is>
-      </c>
-      <c r="G471" t="n">
-        <v>8</v>
-      </c>
-      <c r="H471" t="n">
-        <v>7</v>
-      </c>
+          <t>Sale kit A4 กระดาษอาร์ตมัน 230gขนาดA4 พิมพ์ 4สี 1หน้า</t>
+        </is>
+      </c>
+      <c r="F471" s="4" t="n"/>
       <c r="I471" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>51 - 500</t>
         </is>
       </c>
       <c r="J471" s="5" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="K471" s="5" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="L471" s="6" t="n">
-        <v>40</v>
+        <v>10.35</v>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>vendor 8</t>
+          <t>vendor 6</t>
         </is>
       </c>
       <c r="N471" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O471" s="6" t="n">
-        <v>40</v>
+        <v>10.35</v>
       </c>
       <c r="P471" s="6" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="Q471" s="6" t="n">
-        <v>95.17</v>
+        <v>15.88</v>
       </c>
       <c r="R471" s="6" t="n"/>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 92, "vendor 8": 40, "vendor 9": 84, "vendor 11": 150, "vendor 13": 95, "vendor 14": 110}</t>
+          <t>{"vendor 6": 10.35, "vendor 8": 18, "vendor 9": 18.9, "vendor 11": 17.5, "vendor 13": 10.5, "vendor 14": 20}</t>
         </is>
       </c>
       <c r="T471" s="4" t="n"/>
       <c r="U471" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-96] Couponขนาด 8x7 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 150 บาท</t>
+          <t>[PrintRate-95] Sale kit A4 กระดาษอาร์ตมัน 230gขนาดA4 พิมพ์ 4สี 1หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 500 ชิ้น | ราคาต่อหน่วย 10.35 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 6 ราย ต่ำสุด 10.35 สูงสุด 20 บาท</t>
         </is>
       </c>
     </row>
@@ -37004,14 +36991,14 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J472" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K472" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L472" s="6" t="n">
         <v>40</v>
@@ -37022,27 +37009,27 @@
         </is>
       </c>
       <c r="N472" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O472" s="6" t="n">
         <v>40</v>
       </c>
       <c r="P472" s="6" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Q472" s="6" t="n">
-        <v>77.78</v>
+        <v>95.17</v>
       </c>
       <c r="R472" s="6" t="n"/>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 8": 40, "vendor 9": 63.9, "vendor 11": 100, "vendor 13": 85, "vendor 14": 100}</t>
+          <t>{"vendor 6": 92, "vendor 8": 40, "vendor 9": 84, "vendor 11": 150, "vendor 13": 95, "vendor 14": 110}</t>
         </is>
       </c>
       <c r="T472" s="4" t="n"/>
       <c r="U472" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-96] Couponขนาด 8x7 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 5 ราย ต่ำสุด 40 สูงสุด 100 บาท</t>
+          <t>[PrintRate-96] Couponขนาด 8x7 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 150 บาท</t>
         </is>
       </c>
     </row>
@@ -37085,14 +37072,14 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J473" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K473" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L473" s="6" t="n">
         <v>40</v>
@@ -37103,34 +37090,34 @@
         </is>
       </c>
       <c r="N473" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O473" s="6" t="n">
         <v>40</v>
       </c>
       <c r="P473" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q473" s="6" t="n">
-        <v>68.33</v>
+        <v>77.78</v>
       </c>
       <c r="R473" s="6" t="n"/>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 69, "vendor 8": 40, "vendor 9": 50.95, "vendor 11": 85, "vendor 13": 75, "vendor 14": 90}</t>
+          <t>{"vendor 8": 40, "vendor 9": 63.9, "vendor 11": 100, "vendor 13": 85, "vendor 14": 100}</t>
         </is>
       </c>
       <c r="T473" s="4" t="n"/>
       <c r="U473" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-96] Couponขนาด 8x7 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 90 บาท</t>
+          <t>[PrintRate-96] Couponขนาด 8x7 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 5 ราย ต่ำสุด 40 สูงสุด 100 บาท</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>PrintRate-97</t>
+          <t>PrintRate-96</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -37145,12 +37132,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Couponขนาด 8x7 cm (100ใบ/เล่ม)</t>
+          <t>Couponขนาด 8x7 cm (50ใบ/เล่ม)</t>
         </is>
       </c>
       <c r="F474" s="4" t="inlineStr">
@@ -37166,17 +37153,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J474" s="5" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="K474" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L474" s="6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M474" t="inlineStr">
         <is>
@@ -37187,24 +37174,24 @@
         <v>6</v>
       </c>
       <c r="O474" s="6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P474" s="6" t="n">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="Q474" s="6" t="n">
-        <v>151.82</v>
+        <v>68.33</v>
       </c>
       <c r="R474" s="6" t="n"/>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 172.5, "vendor 8": 80, "vendor 9": 113.4, "vendor 11": 150, "vendor 13": 175, "vendor 14": 220}</t>
+          <t>{"vendor 6": 69, "vendor 8": 40, "vendor 9": 50.95, "vendor 11": 85, "vendor 13": 75, "vendor 14": 90}</t>
         </is>
       </c>
       <c r="T474" s="4" t="n"/>
       <c r="U474" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-97] Couponขนาด 8x7 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 220 บาท</t>
+          <t>[PrintRate-96] Couponขนาด 8x7 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 90 บาท</t>
         </is>
       </c>
     </row>
@@ -37247,14 +37234,14 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J475" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K475" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L475" s="6" t="n">
         <v>80</v>
@@ -37271,21 +37258,21 @@
         <v>80</v>
       </c>
       <c r="P475" s="6" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="Q475" s="6" t="n">
-        <v>130.96</v>
+        <v>151.82</v>
       </c>
       <c r="R475" s="6" t="n"/>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 149.5, "vendor 8": 80, "vendor 9": 86.27, "vendor 11": 100, "vendor 13": 170, "vendor 14": 200}</t>
+          <t>{"vendor 6": 172.5, "vendor 8": 80, "vendor 9": 113.4, "vendor 11": 150, "vendor 13": 175, "vendor 14": 220}</t>
         </is>
       </c>
       <c r="T475" s="4" t="n"/>
       <c r="U475" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-97] Couponขนาด 8x7 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 200 บาท</t>
+          <t>[PrintRate-97] Couponขนาด 8x7 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 220 บาท</t>
         </is>
       </c>
     </row>
@@ -37328,52 +37315,52 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J476" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K476" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L476" s="6" t="n">
-        <v>68.78</v>
+        <v>80</v>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 8</t>
         </is>
       </c>
       <c r="N476" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O476" s="6" t="n">
-        <v>68.78</v>
+        <v>80</v>
       </c>
       <c r="P476" s="6" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="Q476" s="6" t="n">
-        <v>115.05</v>
+        <v>130.96</v>
       </c>
       <c r="R476" s="6" t="n"/>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 126.5, "vendor 8": 80, "vendor 9": 68.78, "vendor 11": 85, "vendor 13": 150, "vendor 14": 180}</t>
+          <t>{"vendor 6": 149.5, "vendor 8": 80, "vendor 9": 86.27, "vendor 11": 100, "vendor 13": 170, "vendor 14": 200}</t>
         </is>
       </c>
       <c r="T476" s="4" t="n"/>
       <c r="U476" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-97] Couponขนาด 8x7 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 68.78 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 68.78 สูงสุด 180 บาท</t>
+          <t>[PrintRate-97] Couponขนาด 8x7 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 200 บาท</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>PrintRate-98</t>
+          <t>PrintRate-97</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -37388,12 +37375,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม)</t>
+          <t>Couponขนาด 8x7 cm (100ใบ/เล่ม)</t>
         </is>
       </c>
       <c r="F477" s="4" t="inlineStr">
@@ -37401,47 +37388,53 @@
           <t>กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม</t>
         </is>
       </c>
+      <c r="G477" t="n">
+        <v>8</v>
+      </c>
+      <c r="H477" t="n">
+        <v>7</v>
+      </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J477" s="5" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="K477" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L477" s="6" t="n">
-        <v>40</v>
+        <v>68.78</v>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>vendor 8</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N477" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O477" s="6" t="n">
-        <v>40</v>
+        <v>68.78</v>
       </c>
       <c r="P477" s="6" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="Q477" s="6" t="n">
-        <v>155.03</v>
+        <v>115.05</v>
       </c>
       <c r="R477" s="6" t="n"/>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 97.75, "vendor 8": 40, "vendor 9": 92.4, "vendor 11": 400, "vendor 13": 180, "vendor 14": 120}</t>
+          <t>{"vendor 6": 126.5, "vendor 8": 80, "vendor 9": 68.78, "vendor 11": 85, "vendor 13": 150, "vendor 14": 180}</t>
         </is>
       </c>
       <c r="T477" s="4" t="n"/>
       <c r="U477" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-98] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 400 บาท</t>
+          <t>[PrintRate-97] Couponขนาด 8x7 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 68.78 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 68.78 สูงสุด 180 บาท</t>
         </is>
       </c>
     </row>
@@ -37478,14 +37471,14 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J478" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K478" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L478" s="6" t="n">
         <v>40</v>
@@ -37502,21 +37495,21 @@
         <v>40</v>
       </c>
       <c r="P478" s="6" t="n">
-        <v>165</v>
+        <v>400</v>
       </c>
       <c r="Q478" s="6" t="n">
-        <v>98.59</v>
+        <v>155.03</v>
       </c>
       <c r="R478" s="6" t="n"/>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 86.25, "vendor 8": 40, "vendor 9": 70.29, "vendor 11": 120, "vendor 13": 165, "vendor 14": 110}</t>
+          <t>{"vendor 6": 97.75, "vendor 8": 40, "vendor 9": 92.4, "vendor 11": 400, "vendor 13": 180, "vendor 14": 120}</t>
         </is>
       </c>
       <c r="T478" s="4" t="n"/>
       <c r="U478" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-98] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 165 บาท</t>
+          <t>[PrintRate-98] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 400 บาท</t>
         </is>
       </c>
     </row>
@@ -37553,14 +37546,14 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J479" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K479" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L479" s="6" t="n">
         <v>40</v>
@@ -37577,28 +37570,28 @@
         <v>40</v>
       </c>
       <c r="P479" s="6" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="Q479" s="6" t="n">
-        <v>86.13</v>
+        <v>98.59</v>
       </c>
       <c r="R479" s="6" t="n"/>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 74.75, "vendor 8": 40, "vendor 9": 56.05, "vendor 11": 90, "vendor 13": 156, "vendor 14": 100}</t>
+          <t>{"vendor 6": 86.25, "vendor 8": 40, "vendor 9": 70.29, "vendor 11": 120, "vendor 13": 165, "vendor 14": 110}</t>
         </is>
       </c>
       <c r="T479" s="4" t="n"/>
       <c r="U479" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-98] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 156 บาท</t>
+          <t>[PrintRate-98] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 165 บาท</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>PrintRate-99</t>
+          <t>PrintRate-98</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -37613,12 +37606,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม)</t>
+          <t>Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม)</t>
         </is>
       </c>
       <c r="F480" s="4" t="inlineStr">
@@ -37628,17 +37621,17 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J480" s="5" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="K480" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L480" s="6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
@@ -37649,24 +37642,24 @@
         <v>6</v>
       </c>
       <c r="O480" s="6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P480" s="6" t="n">
-        <v>400</v>
+        <v>156</v>
       </c>
       <c r="Q480" s="6" t="n">
-        <v>199.93</v>
+        <v>86.13</v>
       </c>
       <c r="R480" s="6" t="n"/>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 178.25, "vendor 8": 80, "vendor 9": 121.34, "vendor 11": 400, "vendor 13": 180, "vendor 14": 240}</t>
+          <t>{"vendor 6": 74.75, "vendor 8": 40, "vendor 9": 56.05, "vendor 11": 90, "vendor 13": 156, "vendor 14": 100}</t>
         </is>
       </c>
       <c r="T480" s="4" t="n"/>
       <c r="U480" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-99] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 400 บาท</t>
+          <t>[PrintRate-98] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (50ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 40 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 40 สูงสุด 156 บาท</t>
         </is>
       </c>
     </row>
@@ -37703,14 +37696,14 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J481" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K481" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L481" s="6" t="n">
         <v>80</v>
@@ -37727,21 +37720,21 @@
         <v>80</v>
       </c>
       <c r="P481" s="6" t="n">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="Q481" s="6" t="n">
-        <v>138.76</v>
+        <v>199.93</v>
       </c>
       <c r="R481" s="6" t="n"/>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 155.25, "vendor 8": 80, "vendor 9": 92.3, "vendor 11": 120, "vendor 13": 165, "vendor 14": 220}</t>
+          <t>{"vendor 6": 178.25, "vendor 8": 80, "vendor 9": 121.34, "vendor 11": 400, "vendor 13": 180, "vendor 14": 240}</t>
         </is>
       </c>
       <c r="T481" s="4" t="n"/>
       <c r="U481" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-99] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 220 บาท</t>
+          <t>[PrintRate-99] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 400 บาท</t>
         </is>
       </c>
     </row>
@@ -37778,52 +37771,52 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J482" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K482" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L482" s="6" t="n">
-        <v>73.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 8</t>
         </is>
       </c>
       <c r="N482" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O482" s="6" t="n">
-        <v>73.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="P482" s="6" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="Q482" s="6" t="n">
-        <v>121.98</v>
+        <v>138.76</v>
       </c>
       <c r="R482" s="6" t="n"/>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 132.25, "vendor 8": 80, "vendor 9": 73.6, "vendor 11": 90, "vendor 13": 156, "vendor 14": 200}</t>
+          <t>{"vendor 6": 155.25, "vendor 8": 80, "vendor 9": 92.3, "vendor 11": 120, "vendor 13": 165, "vendor 14": 220}</t>
         </is>
       </c>
       <c r="T482" s="4" t="n"/>
       <c r="U482" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-99] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 73.6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 73.6 สูงสุด 200 บาท</t>
+          <t>[PrintRate-99] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 80 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 80 สูงสุด 220 บาท</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>PrintRate-100</t>
+          <t>PrintRate-99</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -37838,28 +37831,32 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>หนังสือคู่มือขนาดA4 อาร์ตมัน120g</t>
-        </is>
-      </c>
-      <c r="F483" s="4" t="n"/>
+          <t>Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม)</t>
+        </is>
+      </c>
+      <c r="F483" s="4" t="inlineStr">
+        <is>
+          <t>กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม</t>
+        </is>
+      </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J483" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K483" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L483" s="6" t="n">
-        <v>76.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M483" t="inlineStr">
         <is>
@@ -37867,27 +37864,27 @@
         </is>
       </c>
       <c r="N483" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O483" s="6" t="n">
-        <v>76.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P483" s="6" t="n">
-        <v>25000</v>
+        <v>200</v>
       </c>
       <c r="Q483" s="6" t="n">
-        <v>6346.68</v>
+        <v>121.98</v>
       </c>
       <c r="R483" s="6" t="n"/>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 8": 130, "vendor 9": 76.7, "vendor 11": 25000, "vendor 15": 180}</t>
+          <t>{"vendor 6": 132.25, "vendor 8": 80, "vendor 9": 73.6, "vendor 11": 90, "vendor 13": 156, "vendor 14": 200}</t>
         </is>
       </c>
       <c r="T483" s="4" t="n"/>
       <c r="U483" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-100] หนังสือคู่มือขนาดA4 อาร์ตมัน120g | หมวด: เรทงานพิมพ์ (Printing Rate) | ที่จำนวน 100 ชิ้น | ราคาต่อหน่วย 76.7 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 4 ราย ต่ำสุด 76.7 สูงสุด 25000 บาท</t>
+          <t>[PrintRate-99] Couponขนาด 3*7 นิ้ว หรืv 10.5*7.5 cm (100ใบ/เล่ม) | รายละเอียด: กระดาษปอนด์ 80g พิมพ์ 2 ด้าน | ด้านหน้า พิมพ์4สี ด้านหลัง พิมพ์1สี ติดกาวเข้าเล่ม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 73.6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 73.6 สูงสุด 200 บาท</t>
         </is>
       </c>
     </row>
@@ -37917,24 +37914,20 @@
           <t>หนังสือคู่มือขนาดA4 อาร์ตมัน120g</t>
         </is>
       </c>
-      <c r="F484" s="4" t="inlineStr">
-        <is>
-          <t>ทั้งเล่มละ 20หน้า พิมพ์ 4สี</t>
-        </is>
-      </c>
+      <c r="F484" s="4" t="n"/>
       <c r="I484" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J484" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K484" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L484" s="6" t="n">
-        <v>71</v>
+        <v>76.7</v>
       </c>
       <c r="M484" t="inlineStr">
         <is>
@@ -37945,24 +37938,24 @@
         <v>4</v>
       </c>
       <c r="O484" s="6" t="n">
-        <v>71</v>
+        <v>76.7</v>
       </c>
       <c r="P484" s="6" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="Q484" s="6" t="n">
-        <v>10089</v>
+        <v>6346.68</v>
       </c>
       <c r="R484" s="6" t="n"/>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 8": 125, "vendor 9": 71, "vendor 11": 40000, "vendor 15": 160}</t>
+          <t>{"vendor 8": 130, "vendor 9": 76.7, "vendor 11": 25000, "vendor 15": 180}</t>
         </is>
       </c>
       <c r="T484" s="4" t="n"/>
       <c r="U484" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-100] หนังสือคู่มือขนาดA4 อาร์ตมัน120g | รายละเอียด: ทั้งเล่มละ 20หน้า พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ที่จำนวน 200 ชิ้น | ราคาต่อหน่วย 71 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 4 ราย ต่ำสุด 71 สูงสุด 40000 บาท</t>
+          <t>[PrintRate-100] หนังสือคู่มือขนาดA4 อาร์ตมัน120g | หมวด: เรทงานพิมพ์ (Printing Rate) | ที่จำนวน 100 ชิ้น | ราคาต่อหน่วย 76.7 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 4 ราย ต่ำสุด 76.7 สูงสุด 25000 บาท</t>
         </is>
       </c>
     </row>
@@ -37994,22 +37987,22 @@
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>ทั้งเล่มละ 20หน้า พิมพ์ 4สี | เคลือบลามิเนทเข้าเล่ม มุงหลังคา</t>
+          <t>ทั้งเล่มละ 20หน้า พิมพ์ 4สี</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J485" s="5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K485" s="5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L485" s="6" t="n">
-        <v>66.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="M485" t="inlineStr">
         <is>
@@ -38020,31 +38013,31 @@
         <v>4</v>
       </c>
       <c r="O485" s="6" t="n">
-        <v>66.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="P485" s="6" t="n">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="Q485" s="6" t="n">
-        <v>11334.23</v>
+        <v>10089</v>
       </c>
       <c r="R485" s="6" t="n"/>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 8": 120, "vendor 9": 66.9, "vendor 11": 45000, "vendor 15": 150}</t>
+          <t>{"vendor 8": 125, "vendor 9": 71, "vendor 11": 40000, "vendor 15": 160}</t>
         </is>
       </c>
       <c r="T485" s="4" t="n"/>
       <c r="U485" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-100] หนังสือคู่มือขนาดA4 อาร์ตมัน120g | รายละเอียด: ทั้งเล่มละ 20หน้า พิมพ์ 4สี | เคลือบลามิเนทเข้าเล่ม มุงหลังคา | หมวด: เรทงานพิมพ์ (Printing Rate) | ที่จำนวน 300 ชิ้น | ราคาต่อหน่วย 66.9 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 4 ราย ต่ำสุด 66.9 สูงสุด 45000 บาท</t>
+          <t>[PrintRate-100] หนังสือคู่มือขนาดA4 อาร์ตมัน120g | รายละเอียด: ทั้งเล่มละ 20หน้า พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ที่จำนวน 200 ชิ้น | ราคาต่อหน่วย 71 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 4 ราย ต่ำสุด 71 สูงสุด 40000 บาท</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>PrintRate-101</t>
+          <t>PrintRate-100</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -38059,56 +38052,60 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า</t>
-        </is>
-      </c>
-      <c r="F486" s="4" t="n"/>
+          <t>หนังสือคู่มือขนาดA4 อาร์ตมัน120g</t>
+        </is>
+      </c>
+      <c r="F486" s="4" t="inlineStr">
+        <is>
+          <t>ทั้งเล่มละ 20หน้า พิมพ์ 4สี | เคลือบลามิเนทเข้าเล่ม มุงหลังคา</t>
+        </is>
+      </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>100 - 500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J486" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K486" s="5" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L486" s="6" t="n">
-        <v>8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>vendor 10</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N486" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O486" s="6" t="n">
-        <v>8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="P486" s="6" t="n">
-        <v>72</v>
+        <v>45000</v>
       </c>
       <c r="Q486" s="6" t="n">
-        <v>33.31</v>
+        <v>11334.23</v>
       </c>
       <c r="R486" s="6" t="n"/>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 32.2, "vendor 9": 19.64, "vendor 10": 8, "vendor 11": 72, "vendor 13": 33, "vendor 14": 35}</t>
+          <t>{"vendor 8": 120, "vendor 9": 66.9, "vendor 11": 45000, "vendor 15": 150}</t>
         </is>
       </c>
       <c r="T486" s="4" t="n"/>
       <c r="U486" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-101] โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 500 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 6 ราย ต่ำสุด 8 สูงสุด 72 บาท</t>
+          <t>[PrintRate-100] หนังสือคู่มือขนาดA4 อาร์ตมัน120g | รายละเอียด: ทั้งเล่มละ 20หน้า พิมพ์ 4สี | เคลือบลามิเนทเข้าเล่ม มุงหลังคา | หมวด: เรทงานพิมพ์ (Printing Rate) | ที่จำนวน 300 ชิ้น | ราคาต่อหน่วย 66.9 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 4 ราย ต่ำสุด 66.9 สูงสุด 45000 บาท</t>
         </is>
       </c>
     </row>
@@ -38141,45 +38138,45 @@
       <c r="F487" s="4" t="n"/>
       <c r="I487" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>100 - 500</t>
         </is>
       </c>
       <c r="J487" s="5" t="n">
-        <v>501</v>
+        <v>100</v>
       </c>
       <c r="K487" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L487" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>vendor 10</t>
+        </is>
+      </c>
+      <c r="N487" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t>vendor 10</t>
-        </is>
-      </c>
-      <c r="N487" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="O487" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P487" s="6" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="Q487" s="6" t="n">
-        <v>20.93</v>
+        <v>33.31</v>
       </c>
       <c r="R487" s="6" t="n"/>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 28.75, "vendor 8": 8, "vendor 9": 12.74, "vendor 10": 6, "vendor 11": 30, "vendor 13": 29, "vendor 14": 32}</t>
+          <t>{"vendor 6": 32.2, "vendor 9": 19.64, "vendor 10": 8, "vendor 11": 72, "vendor 13": 33, "vendor 14": 35}</t>
         </is>
       </c>
       <c r="T487" s="4" t="n"/>
       <c r="U487" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-101] โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 32 บาท</t>
+          <t>[PrintRate-101] โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 500 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 6 ราย ต่ำสุด 8 สูงสุด 72 บาท</t>
         </is>
       </c>
     </row>
@@ -38212,17 +38209,17 @@
       <c r="F488" s="4" t="n"/>
       <c r="I488" t="inlineStr">
         <is>
-          <t>1,001 - 2,000</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J488" s="5" t="n">
-        <v>1001</v>
+        <v>501</v>
       </c>
       <c r="K488" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="L488" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M488" t="inlineStr">
         <is>
@@ -38233,31 +38230,31 @@
         <v>7</v>
       </c>
       <c r="O488" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P488" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q488" s="6" t="n">
-        <v>17.69</v>
+        <v>20.93</v>
       </c>
       <c r="R488" s="6" t="n"/>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 27.6, "vendor 8": 6, "vendor 9": 9.24, "vendor 10": 5, "vendor 11": 18, "vendor 13": 28, "vendor 14": 30}</t>
+          <t>{"vendor 6": 28.75, "vendor 8": 8, "vendor 9": 12.74, "vendor 10": 6, "vendor 11": 30, "vendor 13": 29, "vendor 14": 32}</t>
         </is>
       </c>
       <c r="T488" s="4" t="n"/>
       <c r="U488" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-101] โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 2,000 ชิ้น | ราคาต่อหน่วย 5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 5 สูงสุด 30 บาท</t>
+          <t>[PrintRate-101] โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 6 สูงสุด 32 บาท</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>PrintRate-102</t>
+          <t>PrintRate-101</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -38272,62 +38269,56 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Vacuum ขนาด 13x15 cm.</t>
+          <t>โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า</t>
         </is>
       </c>
       <c r="F489" s="4" t="n"/>
-      <c r="G489" t="n">
-        <v>13</v>
-      </c>
-      <c r="H489" t="n">
-        <v>15</v>
-      </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>1,000 - 5,000</t>
+          <t>1,001 - 2,000</t>
         </is>
       </c>
       <c r="J489" s="5" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K489" s="5" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="L489" s="6" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>vendor 8</t>
+          <t>vendor 10</t>
         </is>
       </c>
       <c r="N489" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O489" s="6" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="P489" s="6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q489" s="6" t="n">
-        <v>7.76</v>
+        <v>17.69</v>
       </c>
       <c r="R489" s="6" t="n"/>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 2": 7, "vendor 6": 5.52, "vendor 8": 2.8, "vendor 9": 5.52, "vendor 10": 5, "vendor 11": 6, "vendor 13": 6, "vendor 14": 10, "vendor 15": 22}</t>
+          <t>{"vendor 6": 27.6, "vendor 8": 6, "vendor 9": 9.24, "vendor 10": 5, "vendor 11": 18, "vendor 13": 28, "vendor 14": 30}</t>
         </is>
       </c>
       <c r="T489" s="4" t="n"/>
       <c r="U489" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-102] Vacuum ขนาด 13x15 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,000 - 5,000 ชิ้น | ราคาต่อหน่วย 2.8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 9 ราย ต่ำสุด 2.8 สูงสุด 22 บาท</t>
+          <t>[PrintRate-101] โปสเตอร์ ขนาด 16 x 24 นิ้ว พิมพ์ 4 สี 1 หน้า | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 2,000 ชิ้น | ราคาต่อหน่วย 5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 10 | มีผู้เสนอราคา 7 ราย ต่ำสุด 5 สูงสุด 30 บาท</t>
         </is>
       </c>
     </row>
@@ -38357,11 +38348,7 @@
           <t>Vacuum ขนาด 13x15 cm.</t>
         </is>
       </c>
-      <c r="F490" s="4" t="inlineStr">
-        <is>
-          <t>สติ๊กเกอร์PVC ขาวกาวรีมูฟ</t>
-        </is>
-      </c>
+      <c r="F490" s="4" t="n"/>
       <c r="G490" t="n">
         <v>13</v>
       </c>
@@ -38370,17 +38357,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>5,001 - 8,000</t>
+          <t>1,000 - 5,000</t>
         </is>
       </c>
       <c r="J490" s="5" t="n">
-        <v>5001</v>
+        <v>1000</v>
       </c>
       <c r="K490" s="5" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="L490" s="6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M490" t="inlineStr">
         <is>
@@ -38391,31 +38378,31 @@
         <v>9</v>
       </c>
       <c r="O490" s="6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P490" s="6" t="n">
         <v>22</v>
       </c>
       <c r="Q490" s="6" t="n">
-        <v>6.74</v>
+        <v>7.76</v>
       </c>
       <c r="R490" s="6" t="n"/>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 2": 6.5, "vendor 6": 4.6, "vendor 8": 2.5, "vendor 9": 3.74, "vendor 10": 4, "vendor 11": 5.5, "vendor 13": 4.8, "vendor 14": 7, "vendor 15": 22}</t>
+          <t>{"vendor 2": 7, "vendor 6": 5.52, "vendor 8": 2.8, "vendor 9": 5.52, "vendor 10": 5, "vendor 11": 6, "vendor 13": 6, "vendor 14": 10, "vendor 15": 22}</t>
         </is>
       </c>
       <c r="T490" s="4" t="n"/>
       <c r="U490" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-102] Vacuum ขนาด 13x15 cm. | รายละเอียด: สติ๊กเกอร์PVC ขาวกาวรีมูฟ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 5,001 - 8,000 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 9 ราย ต่ำสุด 2.5 สูงสุด 22 บาท</t>
+          <t>[PrintRate-102] Vacuum ขนาด 13x15 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,000 - 5,000 ชิ้น | ราคาต่อหน่วย 2.8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 9 ราย ต่ำสุด 2.8 สูงสุด 22 บาท</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>PrintRate-103</t>
+          <t>PrintRate-102</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -38430,56 +38417,66 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Head PM Rack</t>
-        </is>
-      </c>
-      <c r="F491" s="4" t="n"/>
+          <t>Vacuum ขนาด 13x15 cm.</t>
+        </is>
+      </c>
+      <c r="F491" s="4" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์PVC ขาวกาวรีมูฟ</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>13</v>
+      </c>
+      <c r="H491" t="n">
+        <v>15</v>
+      </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>1,000 - 3,000</t>
+          <t>5,001 - 8,000</t>
         </is>
       </c>
       <c r="J491" s="5" t="n">
-        <v>1000</v>
+        <v>5001</v>
       </c>
       <c r="K491" s="5" t="n">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="L491" s="6" t="n">
-        <v>18</v>
+        <v>2.5</v>
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>vendor 2</t>
+          <t>vendor 8</t>
         </is>
       </c>
       <c r="N491" s="5" t="n">
         <v>9</v>
       </c>
       <c r="O491" s="6" t="n">
-        <v>18</v>
+        <v>2.5</v>
       </c>
       <c r="P491" s="6" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="Q491" s="6" t="n">
-        <v>28.42</v>
+        <v>6.74</v>
       </c>
       <c r="R491" s="6" t="n"/>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 2": 18, "vendor 5": 35, "vendor 6": 25.3, "vendor 9": 19, "vendor 10": 25, "vendor 11": 38, "vendor 13": 25.5, "vendor 14": 25, "vendor 15": 45}</t>
+          <t>{"vendor 2": 6.5, "vendor 6": 4.6, "vendor 8": 2.5, "vendor 9": 3.74, "vendor 10": 4, "vendor 11": 5.5, "vendor 13": 4.8, "vendor 14": 7, "vendor 15": 22}</t>
         </is>
       </c>
       <c r="T491" s="4" t="n"/>
       <c r="U491" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-103] Head PM Rack | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,000 - 3,000 ชิ้น | ราคาต่อหน่วย 18 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 9 ราย ต่ำสุด 18 สูงสุด 45 บาท</t>
+          <t>[PrintRate-102] Vacuum ขนาด 13x15 cm. | รายละเอียด: สติ๊กเกอร์PVC ขาวกาวรีมูฟ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 5,001 - 8,000 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 9 ราย ต่ำสุด 2.5 สูงสุด 22 บาท</t>
         </is>
       </c>
     </row>
@@ -38509,30 +38506,20 @@
           <t>Head PM Rack</t>
         </is>
       </c>
-      <c r="F492" s="4" t="inlineStr">
-        <is>
-          <t>ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC</t>
-        </is>
-      </c>
-      <c r="G492" t="n">
-        <v>42</v>
-      </c>
-      <c r="H492" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="F492" s="4" t="n"/>
       <c r="I492" t="inlineStr">
         <is>
-          <t>3,001 - 5,000</t>
+          <t>1,000 - 3,000</t>
         </is>
       </c>
       <c r="J492" s="5" t="n">
-        <v>3001</v>
+        <v>1000</v>
       </c>
       <c r="K492" s="5" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="L492" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M492" t="inlineStr">
         <is>
@@ -38540,27 +38527,27 @@
         </is>
       </c>
       <c r="N492" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O492" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P492" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q492" s="6" t="n">
-        <v>26.48</v>
+        <v>28.42</v>
       </c>
       <c r="R492" s="6" t="n"/>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 2": 17, "vendor 6": 25.3, "vendor 9": 18, "vendor 10": 25, "vendor 11": 35, "vendor 13": 25.5, "vendor 14": 24, "vendor 15": 42}</t>
+          <t>{"vendor 2": 18, "vendor 5": 35, "vendor 6": 25.3, "vendor 9": 19, "vendor 10": 25, "vendor 11": 38, "vendor 13": 25.5, "vendor 14": 25, "vendor 15": 45}</t>
         </is>
       </c>
       <c r="T492" s="4" t="n"/>
       <c r="U492" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-103] Head PM Rack | รายละเอียด: ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 3,001 - 5,000 ชิ้น | ราคาต่อหน่วย 17 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 8 ราย ต่ำสุด 17 สูงสุด 42 บาท</t>
+          <t>[PrintRate-103] Head PM Rack | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,000 - 3,000 ชิ้น | ราคาต่อหน่วย 18 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 9 ราย ต่ำสุด 18 สูงสุด 45 บาท</t>
         </is>
       </c>
     </row>
@@ -38603,17 +38590,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>5,001 - 8,000</t>
+          <t>3,001 - 5,000</t>
         </is>
       </c>
       <c r="J493" s="5" t="n">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="K493" s="5" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="L493" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M493" t="inlineStr">
         <is>
@@ -38624,24 +38611,24 @@
         <v>8</v>
       </c>
       <c r="O493" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P493" s="6" t="n">
-        <v>2525</v>
+        <v>42</v>
       </c>
       <c r="Q493" s="6" t="n">
-        <v>337.62</v>
+        <v>26.48</v>
       </c>
       <c r="R493" s="6" t="n"/>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 2": 16, "vendor 6": 23, "vendor 9": 17, "vendor 10": 2525, "vendor 11": 33, "vendor 13": 24, "vendor 14": 23, "vendor 15": 40}</t>
+          <t>{"vendor 2": 17, "vendor 6": 25.3, "vendor 9": 18, "vendor 10": 25, "vendor 11": 35, "vendor 13": 25.5, "vendor 14": 24, "vendor 15": 42}</t>
         </is>
       </c>
       <c r="T493" s="4" t="n"/>
       <c r="U493" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-103] Head PM Rack | รายละเอียด: ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 5,001 - 8,000 ชิ้น | ราคาต่อหน่วย 16 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 8 ราย ต่ำสุด 16 สูงสุด 2525 บาท</t>
+          <t>[PrintRate-103] Head PM Rack | รายละเอียด: ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 3,001 - 5,000 ชิ้น | ราคาต่อหน่วย 17 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 8 ราย ต่ำสุด 17 สูงสุด 42 บาท</t>
         </is>
       </c>
     </row>
@@ -38684,17 +38671,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>8,001 - 10,000</t>
+          <t>5,001 - 8,000</t>
         </is>
       </c>
       <c r="J494" s="5" t="n">
-        <v>8001</v>
+        <v>5001</v>
       </c>
       <c r="K494" s="5" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="L494" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M494" t="inlineStr">
         <is>
@@ -38705,31 +38692,31 @@
         <v>8</v>
       </c>
       <c r="O494" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P494" s="6" t="n">
-        <v>38</v>
+        <v>2525</v>
       </c>
       <c r="Q494" s="6" t="n">
-        <v>24.25</v>
+        <v>337.62</v>
       </c>
       <c r="R494" s="6" t="n"/>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 2": 15, "vendor 6": 23, "vendor 9": 16, "vendor 10": 25, "vendor 11": 32, "vendor 13": 23, "vendor 14": 22, "vendor 15": 38}</t>
+          <t>{"vendor 2": 16, "vendor 6": 23, "vendor 9": 17, "vendor 10": 2525, "vendor 11": 33, "vendor 13": 24, "vendor 14": 23, "vendor 15": 40}</t>
         </is>
       </c>
       <c r="T494" s="4" t="n"/>
       <c r="U494" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-103] Head PM Rack | รายละเอียด: ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 8,001 - 10,000 ชิ้น | ราคาต่อหน่วย 15 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 8 ราย ต่ำสุด 15 สูงสุด 38 บาท</t>
+          <t>[PrintRate-103] Head PM Rack | รายละเอียด: ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 5,001 - 8,000 ชิ้น | ราคาต่อหน่วย 16 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 8 ราย ต่ำสุด 16 สูงสุด 2525 บาท</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>PrintRate-104</t>
+          <t>PrintRate-103</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -38744,54 +38731,73 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Hand prop PP board มิล ไดคัท พร้อมด้ามจับท่อ PVC</t>
-        </is>
-      </c>
-      <c r="F495" s="4" t="n"/>
-      <c r="J495" s="5" t="n"/>
-      <c r="K495" s="5" t="n"/>
+          <t>Head PM Rack</t>
+        </is>
+      </c>
+      <c r="F495" s="4" t="inlineStr">
+        <is>
+          <t>ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>42</v>
+      </c>
+      <c r="H495" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>8,001 - 10,000</t>
+        </is>
+      </c>
+      <c r="J495" s="5" t="n">
+        <v>8001</v>
+      </c>
+      <c r="K495" s="5" t="n">
+        <v>10000</v>
+      </c>
       <c r="L495" s="6" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 2</t>
         </is>
       </c>
       <c r="N495" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O495" s="6" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="P495" s="6" t="n">
-        <v>800</v>
+        <v>38</v>
       </c>
       <c r="Q495" s="6" t="n">
-        <v>442.5</v>
+        <v>24.25</v>
       </c>
       <c r="R495" s="6" t="n"/>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 5": 400, "vendor 6": 402.5, "vendor 9": 150, "vendor 10": 500, "vendor 11": 800, "vendor 13": 402.5}</t>
+          <t>{"vendor 2": 15, "vendor 6": 23, "vendor 9": 16, "vendor 10": 25, "vendor 11": 32, "vendor 13": 23, "vendor 14": 22, "vendor 15": 38}</t>
         </is>
       </c>
       <c r="T495" s="4" t="n"/>
       <c r="U495" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-104] Hand prop PP board มิล ไดคัท พร้อมด้ามจับท่อ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 150 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 150 สูงสุด 800 บาท</t>
+          <t>[PrintRate-103] Head PM Rack | รายละเอียด: ขนาด 42x23.8 cm. PP Board 3mm สติ๊กเกอร์ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 8,001 - 10,000 ชิ้น | ราคาต่อหน่วย 15 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 2 | มีผู้เสนอราคา 8 ราย ต่ำสุด 15 สูงสุด 38 บาท</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>PrintRate-105</t>
+          <t>PrintRate-104</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -38806,62 +38812,47 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Sticker Cool Zone ขนาด 20x4cm</t>
+          <t>Hand prop PP board มิล ไดคัท พร้อมด้ามจับท่อ PVC</t>
         </is>
       </c>
       <c r="F496" s="4" t="n"/>
-      <c r="G496" t="n">
-        <v>20</v>
-      </c>
-      <c r="H496" t="n">
-        <v>4</v>
-      </c>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>1 - 5,000</t>
-        </is>
-      </c>
-      <c r="J496" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K496" s="5" t="n">
-        <v>5000</v>
-      </c>
+      <c r="J496" s="5" t="n"/>
+      <c r="K496" s="5" t="n"/>
       <c r="L496" s="6" t="n">
-        <v>3.2</v>
+        <v>150</v>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>vendor 11</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N496" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O496" s="6" t="n">
-        <v>3.2</v>
+        <v>150</v>
       </c>
       <c r="P496" s="6" t="n">
-        <v>28</v>
+        <v>800</v>
       </c>
       <c r="Q496" s="6" t="n">
-        <v>10.23</v>
+        <v>442.5</v>
       </c>
       <c r="R496" s="6" t="n"/>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 4.6, "vendor 9": 6, "vendor 11": 3.2, "vendor 13": 4.6, "vendor 14": 15, "vendor 15": 28}</t>
+          <t>{"vendor 5": 400, "vendor 6": 402.5, "vendor 9": 150, "vendor 10": 500, "vendor 11": 800, "vendor 13": 402.5}</t>
         </is>
       </c>
       <c r="T496" s="4" t="n"/>
       <c r="U496" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 5,000 ชิ้น | ราคาต่อหน่วย 3.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 3.2 สูงสุด 28 บาท</t>
+          <t>[PrintRate-104] Hand prop PP board มิล ไดคัท พร้อมด้ามจับท่อ PVC | หมวด: เรทงานพิมพ์ (Printing Rate) | ราคาต่อหน่วย 150 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 150 สูงสุด 800 บาท</t>
         </is>
       </c>
     </row>
@@ -38891,11 +38882,7 @@
           <t>Sticker Cool Zone ขนาด 20x4cm</t>
         </is>
       </c>
-      <c r="F497" s="4" t="inlineStr">
-        <is>
-          <t>วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์</t>
-        </is>
-      </c>
+      <c r="F497" s="4" t="n"/>
       <c r="G497" t="n">
         <v>20</v>
       </c>
@@ -38904,17 +38891,17 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>5,001 - 10,000</t>
+          <t>1 - 5,000</t>
         </is>
       </c>
       <c r="J497" s="5" t="n">
-        <v>5001</v>
+        <v>1</v>
       </c>
       <c r="K497" s="5" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="L497" s="6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M497" t="inlineStr">
         <is>
@@ -38925,24 +38912,24 @@
         <v>6</v>
       </c>
       <c r="O497" s="6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P497" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q497" s="6" t="n">
-        <v>7.74</v>
+        <v>10.23</v>
       </c>
       <c r="R497" s="6" t="n"/>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 3.75, "vendor 9": 3.3, "vendor 11": 3, "vendor 13": 4.4, "vendor 14": 8, "vendor 15": 24}</t>
+          <t>{"vendor 6": 4.6, "vendor 9": 6, "vendor 11": 3.2, "vendor 13": 4.6, "vendor 14": 15, "vendor 15": 28}</t>
         </is>
       </c>
       <c r="T497" s="4" t="n"/>
       <c r="U497" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | รายละเอียด: วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 5,001 - 10,000 ชิ้น | ราคาต่อหน่วย 3 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 3 สูงสุด 24 บาท</t>
+          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 5,000 ชิ้น | ราคาต่อหน่วย 3.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 3.2 สูงสุด 28 บาท</t>
         </is>
       </c>
     </row>
@@ -38974,7 +38961,7 @@
       </c>
       <c r="F498" s="4" t="inlineStr">
         <is>
-          <t>วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | 4/0 จำนวน 1หน้า ตัดสี่เหลี่ยม</t>
+          <t>วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์</t>
         </is>
       </c>
       <c r="G498" t="n">
@@ -38985,45 +38972,45 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>10,001 - 15,000</t>
+          <t>5,001 - 10,000</t>
         </is>
       </c>
       <c r="J498" s="5" t="n">
-        <v>10001</v>
+        <v>5001</v>
       </c>
       <c r="K498" s="5" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="L498" s="6" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 11</t>
         </is>
       </c>
       <c r="N498" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O498" s="6" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="P498" s="6" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="Q498" s="6" t="n">
-        <v>6.86</v>
+        <v>7.74</v>
       </c>
       <c r="R498" s="6" t="n"/>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 3.45, "vendor 9": 1.92, "vendor 11": 2.8, "vendor 13": 3.5, "vendor 14": 7, "vendor 15": 22.5}</t>
+          <t>{"vendor 6": 3.75, "vendor 9": 3.3, "vendor 11": 3, "vendor 13": 4.4, "vendor 14": 8, "vendor 15": 24}</t>
         </is>
       </c>
       <c r="T498" s="4" t="n"/>
       <c r="U498" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | รายละเอียด: วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | 4/0 จำนวน 1หน้า ตัดสี่เหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 10,001 - 15,000 ชิ้น | ราคาต่อหน่วย 1.92 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 1.92 สูงสุด 22.5 บาท</t>
+          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | รายละเอียด: วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 5,001 - 10,000 ชิ้น | ราคาต่อหน่วย 3 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 3 สูงสุด 24 บาท</t>
         </is>
       </c>
     </row>
@@ -39066,17 +39053,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>15,001 - 20,000</t>
+          <t>10,001 - 15,000</t>
         </is>
       </c>
       <c r="J499" s="5" t="n">
-        <v>15001</v>
+        <v>10001</v>
       </c>
       <c r="K499" s="5" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="L499" s="6" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="M499" t="inlineStr">
         <is>
@@ -39087,31 +39074,31 @@
         <v>6</v>
       </c>
       <c r="O499" s="6" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="P499" s="6" t="n">
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="Q499" s="6" t="n">
-        <v>5.97</v>
+        <v>6.86</v>
       </c>
       <c r="R499" s="6" t="n"/>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 2.88, "vendor 9": 1.36, "vendor 11": 2.6, "vendor 13": 3, "vendor 14": 5, "vendor 15": 21}</t>
+          <t>{"vendor 6": 3.45, "vendor 9": 1.92, "vendor 11": 2.8, "vendor 13": 3.5, "vendor 14": 7, "vendor 15": 22.5}</t>
         </is>
       </c>
       <c r="T499" s="4" t="n"/>
       <c r="U499" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | รายละเอียด: วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | 4/0 จำนวน 1หน้า ตัดสี่เหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 15,001 - 20,000 ชิ้น | ราคาต่อหน่วย 1.36 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 1.36 สูงสุด 21 บาท</t>
+          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | รายละเอียด: วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | 4/0 จำนวน 1หน้า ตัดสี่เหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 10,001 - 15,000 ชิ้น | ราคาต่อหน่วย 1.92 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 1.92 สูงสุด 22.5 บาท</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>PrintRate-106</t>
+          <t>PrintRate-105</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -39126,28 +39113,38 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>ประกาศนียบัตรยุวชน A4 การ์ดขาว210g</t>
-        </is>
-      </c>
-      <c r="F500" s="4" t="n"/>
+          <t>Sticker Cool Zone ขนาด 20x4cm</t>
+        </is>
+      </c>
+      <c r="F500" s="4" t="inlineStr">
+        <is>
+          <t>วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | 4/0 จำนวน 1หน้า ตัดสี่เหลี่ยม</t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>20</v>
+      </c>
+      <c r="H500" t="n">
+        <v>4</v>
+      </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>1 - 50</t>
+          <t>15,001 - 20,000</t>
         </is>
       </c>
       <c r="J500" s="5" t="n">
-        <v>1</v>
+        <v>15001</v>
       </c>
       <c r="K500" s="5" t="n">
-        <v>50</v>
+        <v>20000</v>
       </c>
       <c r="L500" s="6" t="n">
-        <v>16.2</v>
+        <v>1.36</v>
       </c>
       <c r="M500" t="inlineStr">
         <is>
@@ -39158,24 +39155,24 @@
         <v>6</v>
       </c>
       <c r="O500" s="6" t="n">
-        <v>16.2</v>
+        <v>1.36</v>
       </c>
       <c r="P500" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q500" s="6" t="n">
-        <v>19.7</v>
+        <v>5.97</v>
       </c>
       <c r="R500" s="6" t="n"/>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 23, "vendor 8": 18, "vendor 9": 16.2, "vendor 11": 20, "vendor 13": 23, "vendor 15": 18}</t>
+          <t>{"vendor 6": 2.88, "vendor 9": 1.36, "vendor 11": 2.6, "vendor 13": 3, "vendor 14": 5, "vendor 15": 21}</t>
         </is>
       </c>
       <c r="T500" s="4" t="n"/>
       <c r="U500" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 50 ชิ้น | ราคาต่อหน่วย 16.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 16.2 สูงสุด 23 บาท</t>
+          <t>[PrintRate-105] Sticker Cool Zone ขนาด 20x4cm | รายละเอียด: วัสดุสติกเกอร์พีวีซีขาวเงากาวรีมูฟ พิมพ์ | 4/0 จำนวน 1หน้า ตัดสี่เหลี่ยม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 15,001 - 20,000 ชิ้น | ราคาต่อหน่วย 1.36 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 1.36 สูงสุด 21 บาท</t>
         </is>
       </c>
     </row>
@@ -39205,52 +39202,48 @@
           <t>ประกาศนียบัตรยุวชน A4 การ์ดขาว210g</t>
         </is>
       </c>
-      <c r="F501" s="4" t="inlineStr">
-        <is>
-          <t>4สี 1ด้าน</t>
-        </is>
-      </c>
+      <c r="F501" s="4" t="n"/>
       <c r="I501" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1 - 50</t>
         </is>
       </c>
       <c r="J501" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K501" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L501" s="6" t="n">
-        <v>11.5</v>
+        <v>16.2</v>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>vendor 6</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N501" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O501" s="6" t="n">
-        <v>11.5</v>
+        <v>16.2</v>
       </c>
       <c r="P501" s="6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q501" s="6" t="n">
-        <v>14.48</v>
+        <v>19.7</v>
       </c>
       <c r="R501" s="6" t="n"/>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 8": 18, "vendor 9": 12.4, "vendor 11": 18, "vendor 13": 12, "vendor 15": 15}</t>
+          <t>{"vendor 6": 23, "vendor 8": 18, "vendor 9": 16.2, "vendor 11": 20, "vendor 13": 23, "vendor 15": 18}</t>
         </is>
       </c>
       <c r="T501" s="4" t="n"/>
       <c r="U501" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 11.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 6 ราย ต่ำสุด 11.5 สูงสุด 18 บาท</t>
+          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1 - 50 ชิ้น | ราคาต่อหน่วย 16.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 16.2 สูงสุด 23 บาท</t>
         </is>
       </c>
     </row>
@@ -39287,45 +39280,45 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J502" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K502" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L502" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 6</t>
         </is>
       </c>
       <c r="N502" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O502" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="P502" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q502" s="6" t="n">
-        <v>14.31</v>
+        <v>14.48</v>
       </c>
       <c r="R502" s="6" t="n"/>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 5": 20, "vendor 6": 11.5, "vendor 8": 18, "vendor 9": 9.2, "vendor 11": 16.5, "vendor 13": 12, "vendor 15": 13}</t>
+          <t>{"vendor 6": 11.5, "vendor 8": 18, "vendor 9": 12.4, "vendor 11": 18, "vendor 13": 12, "vendor 15": 15}</t>
         </is>
       </c>
       <c r="T502" s="4" t="n"/>
       <c r="U502" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 9.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 9.2 สูงสุด 20 บาท</t>
+          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 11.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 6 | มีผู้เสนอราคา 6 ราย ต่ำสุด 11.5 สูงสุด 18 บาท</t>
         </is>
       </c>
     </row>
@@ -39362,17 +39355,17 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>201 - 500</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J503" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="K503" s="5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L503" s="6" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M503" t="inlineStr">
         <is>
@@ -39380,27 +39373,27 @@
         </is>
       </c>
       <c r="N503" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O503" s="6" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P503" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q503" s="6" t="n">
-        <v>11.82</v>
+        <v>14.31</v>
       </c>
       <c r="R503" s="6" t="n"/>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 9.2, "vendor 8": 18, "vendor 9": 7.5, "vendor 11": 15, "vendor 13": 9.2, "vendor 15": 12}</t>
+          <t>{"vendor 5": 20, "vendor 6": 11.5, "vendor 8": 18, "vendor 9": 9.2, "vendor 11": 16.5, "vendor 13": 12, "vendor 15": 13}</t>
         </is>
       </c>
       <c r="T503" s="4" t="n"/>
       <c r="U503" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 7.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 7.5 สูงสุด 18 บาท</t>
+          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 9.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 7 ราย ต่ำสุด 9.2 สูงสุด 20 บาท</t>
         </is>
       </c>
     </row>
@@ -39437,17 +39430,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>201 - 500</t>
         </is>
       </c>
       <c r="J504" s="5" t="n">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="K504" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L504" s="6" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="M504" t="inlineStr">
         <is>
@@ -39458,31 +39451,31 @@
         <v>6</v>
       </c>
       <c r="O504" s="6" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="P504" s="6" t="n">
         <v>18</v>
       </c>
       <c r="Q504" s="6" t="n">
-        <v>10.33</v>
+        <v>11.82</v>
       </c>
       <c r="R504" s="6" t="n"/>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 8.05, "vendor 8": 18, "vendor 9": 6.9, "vendor 11": 10, "vendor 13": 9, "vendor 15": 10}</t>
+          <t>{"vendor 6": 9.2, "vendor 8": 18, "vendor 9": 7.5, "vendor 11": 15, "vendor 13": 9.2, "vendor 15": 12}</t>
         </is>
       </c>
       <c r="T504" s="4" t="n"/>
       <c r="U504" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 6.9 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 6.9 สูงสุด 18 บาท</t>
+          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 7.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 7.5 สูงสุด 18 บาท</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>PrintRate-107</t>
+          <t>PrintRate-106</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -39497,62 +39490,60 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>AD CARD ขนาด9x13 cm คนละ Aw</t>
-        </is>
-      </c>
-      <c r="F505" s="4" t="n"/>
-      <c r="G505" t="n">
-        <v>9</v>
-      </c>
-      <c r="H505" t="n">
-        <v>13</v>
+          <t>ประกาศนียบัตรยุวชน A4 การ์ดขาว210g</t>
+        </is>
+      </c>
+      <c r="F505" s="4" t="inlineStr">
+        <is>
+          <t>4สี 1ด้าน</t>
+        </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J505" s="5" t="n">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="K505" s="5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="L505" s="6" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>vendor 8</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N505" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O505" s="6" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="P505" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q505" s="6" t="n">
-        <v>9.25</v>
+        <v>10.33</v>
       </c>
       <c r="R505" s="6" t="n"/>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 8": 2.5, "vendor 9": 9, "vendor 11": 4.5, "vendor 13": 12, "vendor 15": 16}</t>
+          <t>{"vendor 6": 8.05, "vendor 8": 18, "vendor 9": 6.9, "vendor 11": 10, "vendor 13": 9, "vendor 15": 10}</t>
         </is>
       </c>
       <c r="T505" s="4" t="n"/>
       <c r="U505" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.5 สูงสุด 16 บาท</t>
+          <t>[PrintRate-106] ประกาศนียบัตรยุวชน A4 การ์ดขาว210g | รายละเอียด: 4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 6.9 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 6.9 สูงสุด 18 บาท</t>
         </is>
       </c>
     </row>
@@ -39582,11 +39573,7 @@
           <t>AD CARD ขนาด9x13 cm คนละ Aw</t>
         </is>
       </c>
-      <c r="F506" s="4" t="inlineStr">
-        <is>
-          <t>การ์ดขาว 210 g4สี 1ด้าน</t>
-        </is>
-      </c>
+      <c r="F506" s="4" t="n"/>
       <c r="G506" t="n">
         <v>9</v>
       </c>
@@ -39595,14 +39582,14 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J506" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K506" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L506" s="6" t="n">
         <v>2.5</v>
@@ -39619,21 +39606,21 @@
         <v>2.5</v>
       </c>
       <c r="P506" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q506" s="6" t="n">
-        <v>8.210000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="R506" s="6" t="n"/>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 8": 2.5, "vendor 9": 5.24, "vendor 11": 4, "vendor 13": 12, "vendor 15": 14}</t>
+          <t>{"vendor 6": 11.5, "vendor 8": 2.5, "vendor 9": 9, "vendor 11": 4.5, "vendor 13": 12, "vendor 15": 16}</t>
         </is>
       </c>
       <c r="T506" s="4" t="n"/>
       <c r="U506" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.5 สูงสุด 14 บาท</t>
+          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.5 สูงสุด 16 บาท</t>
         </is>
       </c>
     </row>
@@ -39676,14 +39663,14 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J507" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K507" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L507" s="6" t="n">
         <v>2.5</v>
@@ -39700,21 +39687,21 @@
         <v>2.5</v>
       </c>
       <c r="P507" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q507" s="6" t="n">
-        <v>6.92</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="R507" s="6" t="n"/>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 9.2, "vendor 8": 2.5, "vendor 9": 3.4, "vendor 11": 3.4, "vendor 13": 10, "vendor 15": 13}</t>
+          <t>{"vendor 6": 11.5, "vendor 8": 2.5, "vendor 9": 5.24, "vendor 11": 4, "vendor 13": 12, "vendor 15": 14}</t>
         </is>
       </c>
       <c r="T507" s="4" t="n"/>
       <c r="U507" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.5 สูงสุด 13 บาท</t>
+          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.5 สูงสุด 14 บาท</t>
         </is>
       </c>
     </row>
@@ -39757,45 +39744,45 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>201 - 500</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J508" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="K508" s="5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L508" s="6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 8</t>
         </is>
       </c>
       <c r="N508" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O508" s="6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="P508" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q508" s="6" t="n">
-        <v>5.38</v>
+        <v>6.92</v>
       </c>
       <c r="R508" s="6" t="n"/>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 6.9, "vendor 8": 2.5, "vendor 9": 2.2, "vendor 11": 3.2, "vendor 13": 7.5, "vendor 15": 10}</t>
+          <t>{"vendor 6": 9.2, "vendor 8": 2.5, "vendor 9": 3.4, "vendor 11": 3.4, "vendor 13": 10, "vendor 15": 13}</t>
         </is>
       </c>
       <c r="T508" s="4" t="n"/>
       <c r="U508" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 2.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.2 สูงสุด 10 บาท</t>
+          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 2.5 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.5 สูงสุด 13 บาท</t>
         </is>
       </c>
     </row>
@@ -39838,17 +39825,17 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>201 - 500</t>
         </is>
       </c>
       <c r="J509" s="5" t="n">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="K509" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L509" s="6" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M509" t="inlineStr">
         <is>
@@ -39859,31 +39846,31 @@
         <v>6</v>
       </c>
       <c r="O509" s="6" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="P509" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q509" s="6" t="n">
-        <v>4.71</v>
+        <v>5.38</v>
       </c>
       <c r="R509" s="6" t="n"/>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 5.75, "vendor 8": 2.5, "vendor 9": 1.98, "vendor 11": 3, "vendor 13": 6, "vendor 15": 9}</t>
+          <t>{"vendor 6": 6.9, "vendor 8": 2.5, "vendor 9": 2.2, "vendor 11": 3.2, "vendor 13": 7.5, "vendor 15": 10}</t>
         </is>
       </c>
       <c r="T509" s="4" t="n"/>
       <c r="U509" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 1.98 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 1.98 สูงสุด 9 บาท</t>
+          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 2.2 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 2.2 สูงสุด 10 บาท</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>PrintRate-108</t>
+          <t>PrintRate-107</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -39898,56 +39885,66 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี</t>
-        </is>
-      </c>
-      <c r="F510" s="4" t="n"/>
+          <t>AD CARD ขนาด9x13 cm คนละ Aw</t>
+        </is>
+      </c>
+      <c r="F510" s="4" t="inlineStr">
+        <is>
+          <t>การ์ดขาว 210 g4สี 1ด้าน</t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>9</v>
+      </c>
+      <c r="H510" t="n">
+        <v>13</v>
+      </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>100 - 500</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J510" s="5" t="n">
-        <v>100</v>
+        <v>501</v>
       </c>
       <c r="K510" s="5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L510" s="6" t="n">
-        <v>0.36</v>
+        <v>1.98</v>
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>vendor 11</t>
+          <t>vendor 9</t>
         </is>
       </c>
       <c r="N510" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O510" s="6" t="n">
-        <v>0.36</v>
+        <v>1.98</v>
       </c>
       <c r="P510" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q510" s="6" t="n">
-        <v>3.73</v>
+        <v>4.71</v>
       </c>
       <c r="R510" s="6" t="n"/>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 5.75, "vendor 8": 1, "vendor 9": 1.3, "vendor 11": 0.36, "vendor 13": 6, "vendor 14": 8}</t>
+          <t>{"vendor 6": 5.75, "vendor 8": 2.5, "vendor 9": 1.98, "vendor 11": 3, "vendor 13": 6, "vendor 15": 9}</t>
         </is>
       </c>
       <c r="T510" s="4" t="n"/>
       <c r="U510" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-108] สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 500 ชิ้น | ราคาต่อหน่วย 0.36 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 0.36 สูงสุด 8 บาท</t>
+          <t>[PrintRate-107] AD CARD ขนาด9x13 cm คนละ Aw | รายละเอียด: การ์ดขาว 210 g4สี 1ด้าน | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 1.98 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 1.98 สูงสุด 9 บาท</t>
         </is>
       </c>
     </row>
@@ -39980,17 +39977,17 @@
       <c r="F511" s="4" t="n"/>
       <c r="I511" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>100 - 500</t>
         </is>
       </c>
       <c r="J511" s="5" t="n">
-        <v>501</v>
+        <v>100</v>
       </c>
       <c r="K511" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L511" s="6" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="M511" t="inlineStr">
         <is>
@@ -40001,24 +39998,24 @@
         <v>6</v>
       </c>
       <c r="O511" s="6" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="P511" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q511" s="6" t="n">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="R511" s="6" t="n"/>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 4.6, "vendor 8": 0.7, "vendor 9": 0.95, "vendor 11": 0.33, "vendor 13": 5, "vendor 14": 7}</t>
+          <t>{"vendor 6": 5.75, "vendor 8": 1, "vendor 9": 1.3, "vendor 11": 0.36, "vendor 13": 6, "vendor 14": 8}</t>
         </is>
       </c>
       <c r="T511" s="4" t="n"/>
       <c r="U511" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-108] สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 0.33 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 0.33 สูงสุด 7 บาท</t>
+          <t>[PrintRate-108] สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 100 - 500 ชิ้น | ราคาต่อหน่วย 0.36 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 0.36 สูงสุด 8 บาท</t>
         </is>
       </c>
     </row>
@@ -40051,17 +40048,17 @@
       <c r="F512" s="4" t="n"/>
       <c r="I512" t="inlineStr">
         <is>
-          <t>1,001 - 2,000</t>
+          <t>501 - 1,000</t>
         </is>
       </c>
       <c r="J512" s="5" t="n">
-        <v>1001</v>
+        <v>501</v>
       </c>
       <c r="K512" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="L512" s="6" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="M512" t="inlineStr">
         <is>
@@ -40072,31 +40069,31 @@
         <v>6</v>
       </c>
       <c r="O512" s="6" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="P512" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q512" s="6" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="R512" s="6" t="n"/>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 3.45, "vendor 8": 0.6, "vendor 9": 0.68, "vendor 11": 0.29, "vendor 13": 3.5, "vendor 14": 6}</t>
+          <t>{"vendor 6": 4.6, "vendor 8": 0.7, "vendor 9": 0.95, "vendor 11": 0.33, "vendor 13": 5, "vendor 14": 7}</t>
         </is>
       </c>
       <c r="T512" s="4" t="n"/>
       <c r="U512" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-108] สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 2,000 ชิ้น | ราคาต่อหน่วย 0.29 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 0.29 สูงสุด 6 บาท</t>
+          <t>[PrintRate-108] สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 0.33 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 0.33 สูงสุด 7 บาท</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>PrintRate-109</t>
+          <t>PrintRate-108</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -40111,62 +40108,56 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Brand menu รูปใบเรือ ขนาด 9x18 cm.</t>
+          <t>สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี</t>
         </is>
       </c>
       <c r="F513" s="4" t="n"/>
-      <c r="G513" t="n">
-        <v>9</v>
-      </c>
-      <c r="H513" t="n">
-        <v>18</v>
-      </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>1,001 - 2,000</t>
         </is>
       </c>
       <c r="J513" s="5" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="K513" s="5" t="n">
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="L513" s="6" t="n">
-        <v>8</v>
+        <v>0.29</v>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>vendor 8</t>
+          <t>vendor 11</t>
         </is>
       </c>
       <c r="N513" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O513" s="6" t="n">
-        <v>8</v>
+        <v>0.29</v>
       </c>
       <c r="P513" s="6" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="Q513" s="6" t="n">
-        <v>19.98</v>
+        <v>2.42</v>
       </c>
       <c r="R513" s="6" t="n"/>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 11.5, "vendor 8": 8, "vendor 9": 18.4, "vendor 11": 25, "vendor 13": 12, "vendor 15": 45}</t>
+          <t>{"vendor 6": 3.45, "vendor 8": 0.6, "vendor 9": 0.68, "vendor 11": 0.29, "vendor 13": 3.5, "vendor 14": 6}</t>
         </is>
       </c>
       <c r="T513" s="4" t="n"/>
       <c r="U513" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 8 สูงสุด 45 บาท</t>
+          <t>[PrintRate-108] สติ๊กเกอร์ PVC วงกลม 3 cm พิมพ์ 4สี | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1,001 - 2,000 ชิ้น | ราคาต่อหน่วย 0.29 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 11 | มีผู้เสนอราคา 6 ราย ต่ำสุด 0.29 สูงสุด 6 บาท</t>
         </is>
       </c>
     </row>
@@ -40196,11 +40187,7 @@
           <t>Brand menu รูปใบเรือ ขนาด 9x18 cm.</t>
         </is>
       </c>
-      <c r="F514" s="4" t="inlineStr">
-        <is>
-          <t>กระดาษอาร์ตมัน 260 แกรม</t>
-        </is>
-      </c>
+      <c r="F514" s="4" t="n"/>
       <c r="G514" t="n">
         <v>9</v>
       </c>
@@ -40209,14 +40196,14 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>51 - 100</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J514" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K514" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L514" s="6" t="n">
         <v>8</v>
@@ -40233,21 +40220,21 @@
         <v>8</v>
       </c>
       <c r="P514" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q514" s="6" t="n">
-        <v>17.3</v>
+        <v>19.98</v>
       </c>
       <c r="R514" s="6" t="n"/>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 9.2, "vendor 8": 8, "vendor 9": 12.6, "vendor 11": 22, "vendor 13": 10, "vendor 15": 42}</t>
+          <t>{"vendor 6": 11.5, "vendor 8": 8, "vendor 9": 18.4, "vendor 11": 25, "vendor 13": 12, "vendor 15": 45}</t>
         </is>
       </c>
       <c r="T514" s="4" t="n"/>
       <c r="U514" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 8 สูงสุด 42 บาท</t>
+          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 1-50 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 8 สูงสุด 45 บาท</t>
         </is>
       </c>
     </row>
@@ -40279,7 +40266,7 @@
       </c>
       <c r="F515" s="4" t="inlineStr">
         <is>
-          <t>กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง</t>
+          <t>กระดาษอาร์ตมัน 260 แกรม</t>
         </is>
       </c>
       <c r="G515" t="n">
@@ -40290,45 +40277,45 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>101 - 200</t>
+          <t>51 - 100</t>
         </is>
       </c>
       <c r="J515" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="K515" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L515" s="6" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>vendor 9</t>
+          <t>vendor 8</t>
         </is>
       </c>
       <c r="N515" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O515" s="6" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="P515" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q515" s="6" t="n">
-        <v>15.8</v>
+        <v>17.3</v>
       </c>
       <c r="R515" s="6" t="n"/>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 9.2, "vendor 8": 8, "vendor 9": 7.62, "vendor 11": 20, "vendor 13": 12, "vendor 15": 38}</t>
+          <t>{"vendor 6": 9.2, "vendor 8": 8, "vendor 9": 12.6, "vendor 11": 22, "vendor 13": 10, "vendor 15": 42}</t>
         </is>
       </c>
       <c r="T515" s="4" t="n"/>
       <c r="U515" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 7.62 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 7.62 สูงสุด 38 บาท</t>
+          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 51 - 100 ชิ้น | ราคาต่อหน่วย 8 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 8 | มีผู้เสนอราคา 6 ราย ต่ำสุด 8 สูงสุด 42 บาท</t>
         </is>
       </c>
     </row>
@@ -40360,7 +40347,7 @@
       </c>
       <c r="F516" s="4" t="inlineStr">
         <is>
-          <t>กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | พิมพ์ 4 สี ,ไดคัทตามแบบ</t>
+          <t>กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง</t>
         </is>
       </c>
       <c r="G516" t="n">
@@ -40371,17 +40358,17 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>201 - 500</t>
+          <t>101 - 200</t>
         </is>
       </c>
       <c r="J516" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="K516" s="5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L516" s="6" t="n">
-        <v>4.6</v>
+        <v>7.62</v>
       </c>
       <c r="M516" t="inlineStr">
         <is>
@@ -40392,24 +40379,24 @@
         <v>6</v>
       </c>
       <c r="O516" s="6" t="n">
-        <v>4.6</v>
+        <v>7.62</v>
       </c>
       <c r="P516" s="6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q516" s="6" t="n">
-        <v>13.61</v>
+        <v>15.8</v>
       </c>
       <c r="R516" s="6" t="n"/>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 8.05, "vendor 8": 8, "vendor 9": 4.6, "vendor 11": 18, "vendor 13": 10, "vendor 15": 33}</t>
+          <t>{"vendor 6": 9.2, "vendor 8": 8, "vendor 9": 7.62, "vendor 11": 20, "vendor 13": 12, "vendor 15": 38}</t>
         </is>
       </c>
       <c r="T516" s="4" t="n"/>
       <c r="U516" s="4" t="inlineStr">
         <is>
-          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | พิมพ์ 4 สี ,ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 4.6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 4.6 สูงสุด 33 บาท</t>
+          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 101 - 200 ชิ้น | ราคาต่อหน่วย 7.62 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 7.62 สูงสุด 38 บาท</t>
         </is>
       </c>
     </row>
@@ -40452,17 +40439,17 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>501 - 1,000</t>
+          <t>201 - 500</t>
         </is>
       </c>
       <c r="J517" s="5" t="n">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="K517" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L517" s="6" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="M517" t="inlineStr">
         <is>
@@ -40473,22 +40460,103 @@
         <v>6</v>
       </c>
       <c r="O517" s="6" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="P517" s="6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q517" s="6" t="n">
-        <v>11.89</v>
+        <v>13.61</v>
       </c>
       <c r="R517" s="6" t="n"/>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>{"vendor 6": 7.48, "vendor 8": 7, "vendor 9": 3.86, "vendor 11": 16, "vendor 13": 8, "vendor 15": 29}</t>
+          <t>{"vendor 6": 8.05, "vendor 8": 8, "vendor 9": 4.6, "vendor 11": 18, "vendor 13": 10, "vendor 15": 33}</t>
         </is>
       </c>
       <c r="T517" s="4" t="n"/>
       <c r="U517" s="4" t="inlineStr">
+        <is>
+          <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | พิมพ์ 4 สี ,ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 201 - 500 ชิ้น | ราคาต่อหน่วย 4.6 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 4.6 สูงสุด 33 บาท</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>PrintRate-109</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>PrintRate</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>เรทงานพิมพ์ (Printing Rate)</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Brand menu รูปใบเรือ ขนาด 9x18 cm.</t>
+        </is>
+      </c>
+      <c r="F518" s="4" t="inlineStr">
+        <is>
+          <t>กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | พิมพ์ 4 สี ,ไดคัทตามแบบ</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>9</v>
+      </c>
+      <c r="H518" t="n">
+        <v>18</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>501 - 1,000</t>
+        </is>
+      </c>
+      <c r="J518" s="5" t="n">
+        <v>501</v>
+      </c>
+      <c r="K518" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L518" s="6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>vendor 9</t>
+        </is>
+      </c>
+      <c r="N518" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O518" s="6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="P518" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q518" s="6" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="R518" s="6" t="n"/>
+      <c r="S518" s="4" t="inlineStr">
+        <is>
+          <t>{"vendor 6": 7.48, "vendor 8": 7, "vendor 9": 3.86, "vendor 11": 16, "vendor 13": 8, "vendor 15": 29}</t>
+        </is>
+      </c>
+      <c r="T518" s="4" t="n"/>
+      <c r="U518" s="4" t="inlineStr">
         <is>
           <t>[PrintRate-109] Brand menu รูปใบเรือ ขนาด 9x18 cm. | รายละเอียด: กระดาษอาร์ตมัน 260 แกรม | เคลือมลามิเนตหน้า-หลัง | พิมพ์ 4 สี ,ไดคัทตามแบบ | หมวด: เรทงานพิมพ์ (Printing Rate) | ช่วงจำนวน 501 - 1,000 ชิ้น | ราคาต่อหน่วย 3.86 บาท (ยังไม่รวม VAT 7%) | ผู้ชนะประมูล: vendor 9 | มีผู้เสนอราคา 6 ราย ต่ำสุด 3.86 สูงสุด 29 บาท</t>
         </is>
@@ -44802,11 +44870,6 @@
       </c>
       <c r="F134" s="6" t="n"/>
       <c r="G134" s="6" t="n"/>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -44827,17 +44890,8 @@
       <c r="E135" t="n">
         <v>1</v>
       </c>
-      <c r="F135" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G135" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>vendor 11</t>
-        </is>
-      </c>
+      <c r="F135" s="6" t="n"/>
+      <c r="G135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -44856,13 +44910,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G136" s="6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -45865,11 +45919,6 @@
       </c>
       <c r="G168" s="6" t="n">
         <v>33</v>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
-        </is>
       </c>
     </row>
     <row r="169">
@@ -46545,7 +46594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -46936,38 +46985,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>พิจารณาราคาตามธงปีกนกที่ได้ซัพพลายเออร์นั้นๆ</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>พิจารณาราคาตามประเภทสินค้าที่ได้ซัพพลายเออร์นั้นๆ</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
   <dataValidations count="1">
-    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ใช่,ไม่ใช่"</formula1>
     </dataValidation>
   </dataValidations>
